--- a/config/BMS_鸿合国轩.xlsx
+++ b/config/BMS_鸿合国轩.xlsx
@@ -11912,7 +11912,7 @@
         <v>19</v>
       </c>
       <c r="H2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>20</v>
@@ -11962,7 +11962,7 @@
         <v>19</v>
       </c>
       <c r="H3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>20</v>
@@ -12012,7 +12012,7 @@
         <v>19</v>
       </c>
       <c r="H4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
@@ -12062,7 +12062,7 @@
         <v>19</v>
       </c>
       <c r="H5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -12112,7 +12112,7 @@
         <v>19</v>
       </c>
       <c r="H6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
@@ -12162,7 +12162,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>20</v>
@@ -12212,7 +12212,7 @@
         <v>19</v>
       </c>
       <c r="H8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>20</v>
@@ -12262,7 +12262,7 @@
         <v>19</v>
       </c>
       <c r="H9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>20</v>
@@ -12312,7 +12312,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>20</v>
@@ -12362,7 +12362,7 @@
         <v>19</v>
       </c>
       <c r="H11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>20</v>
@@ -12412,7 +12412,7 @@
         <v>19</v>
       </c>
       <c r="H12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>20</v>
@@ -12462,7 +12462,7 @@
         <v>19</v>
       </c>
       <c r="H13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>20</v>
@@ -12512,7 +12512,7 @@
         <v>19</v>
       </c>
       <c r="H14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>20</v>
@@ -12562,7 +12562,7 @@
         <v>19</v>
       </c>
       <c r="H15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>20</v>
@@ -12612,7 +12612,7 @@
         <v>19</v>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>20</v>
@@ -12662,7 +12662,7 @@
         <v>19</v>
       </c>
       <c r="H17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>20</v>
@@ -12712,7 +12712,7 @@
         <v>19</v>
       </c>
       <c r="H18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>20</v>
@@ -12762,7 +12762,7 @@
         <v>19</v>
       </c>
       <c r="H19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>20</v>
@@ -12812,7 +12812,7 @@
         <v>19</v>
       </c>
       <c r="H20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>20</v>
@@ -12862,7 +12862,7 @@
         <v>19</v>
       </c>
       <c r="H21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>20</v>
@@ -12912,7 +12912,7 @@
         <v>19</v>
       </c>
       <c r="H22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>20</v>
@@ -12962,7 +12962,7 @@
         <v>19</v>
       </c>
       <c r="H23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>20</v>
@@ -13012,7 +13012,7 @@
         <v>19</v>
       </c>
       <c r="H24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>20</v>
@@ -13062,7 +13062,7 @@
         <v>19</v>
       </c>
       <c r="H25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>20</v>
@@ -13112,7 +13112,7 @@
         <v>19</v>
       </c>
       <c r="H26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>20</v>
@@ -13162,7 +13162,7 @@
         <v>19</v>
       </c>
       <c r="H27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>20</v>
@@ -13212,7 +13212,7 @@
         <v>19</v>
       </c>
       <c r="H28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>20</v>
@@ -13262,7 +13262,7 @@
         <v>19</v>
       </c>
       <c r="H29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>20</v>
@@ -13312,7 +13312,7 @@
         <v>19</v>
       </c>
       <c r="H30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>20</v>
@@ -13362,7 +13362,7 @@
         <v>19</v>
       </c>
       <c r="H31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>20</v>
@@ -13412,7 +13412,7 @@
         <v>19</v>
       </c>
       <c r="H32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>20</v>
@@ -13462,7 +13462,7 @@
         <v>19</v>
       </c>
       <c r="H33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>20</v>
@@ -13512,7 +13512,7 @@
         <v>19</v>
       </c>
       <c r="H34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>20</v>
@@ -13562,7 +13562,7 @@
         <v>19</v>
       </c>
       <c r="H35" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>20</v>
@@ -13612,7 +13612,7 @@
         <v>19</v>
       </c>
       <c r="H36" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>20</v>
@@ -13662,7 +13662,7 @@
         <v>19</v>
       </c>
       <c r="H37" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>20</v>
@@ -13712,7 +13712,7 @@
         <v>19</v>
       </c>
       <c r="H38" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>20</v>
@@ -13762,7 +13762,7 @@
         <v>19</v>
       </c>
       <c r="H39" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>20</v>
@@ -13812,7 +13812,7 @@
         <v>19</v>
       </c>
       <c r="H40" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>20</v>
@@ -13862,7 +13862,7 @@
         <v>19</v>
       </c>
       <c r="H41" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>20</v>
@@ -13912,7 +13912,7 @@
         <v>19</v>
       </c>
       <c r="H42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>20</v>
@@ -13962,7 +13962,7 @@
         <v>19</v>
       </c>
       <c r="H43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>20</v>
@@ -14012,7 +14012,7 @@
         <v>19</v>
       </c>
       <c r="H44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>20</v>
@@ -14062,7 +14062,7 @@
         <v>19</v>
       </c>
       <c r="H45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>20</v>
@@ -14112,7 +14112,7 @@
         <v>19</v>
       </c>
       <c r="H46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>20</v>
@@ -14162,7 +14162,7 @@
         <v>19</v>
       </c>
       <c r="H47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>20</v>
@@ -14212,7 +14212,7 @@
         <v>19</v>
       </c>
       <c r="H48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>20</v>
@@ -14262,7 +14262,7 @@
         <v>19</v>
       </c>
       <c r="H49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>20</v>
@@ -14312,7 +14312,7 @@
         <v>19</v>
       </c>
       <c r="H50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>20</v>
@@ -14362,7 +14362,7 @@
         <v>19</v>
       </c>
       <c r="H51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>20</v>
@@ -14412,7 +14412,7 @@
         <v>19</v>
       </c>
       <c r="H52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>20</v>
@@ -14462,7 +14462,7 @@
         <v>19</v>
       </c>
       <c r="H53" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>20</v>
@@ -14512,7 +14512,7 @@
         <v>19</v>
       </c>
       <c r="H54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>20</v>
@@ -14562,7 +14562,7 @@
         <v>19</v>
       </c>
       <c r="H55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>20</v>
@@ -14612,7 +14612,7 @@
         <v>19</v>
       </c>
       <c r="H56" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>20</v>
@@ -14662,7 +14662,7 @@
         <v>19</v>
       </c>
       <c r="H57" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>20</v>
@@ -14712,7 +14712,7 @@
         <v>19</v>
       </c>
       <c r="H58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>20</v>
@@ -14762,7 +14762,7 @@
         <v>19</v>
       </c>
       <c r="H59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>20</v>
@@ -14812,7 +14812,7 @@
         <v>19</v>
       </c>
       <c r="H60" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>20</v>
@@ -14862,7 +14862,7 @@
         <v>19</v>
       </c>
       <c r="H61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>20</v>
@@ -14912,7 +14912,7 @@
         <v>19</v>
       </c>
       <c r="H62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>20</v>
@@ -14962,7 +14962,7 @@
         <v>19</v>
       </c>
       <c r="H63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>20</v>
@@ -15012,7 +15012,7 @@
         <v>19</v>
       </c>
       <c r="H64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>20</v>
@@ -15062,7 +15062,7 @@
         <v>19</v>
       </c>
       <c r="H65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>20</v>
@@ -15112,7 +15112,7 @@
         <v>19</v>
       </c>
       <c r="H66" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>20</v>
@@ -15162,7 +15162,7 @@
         <v>19</v>
       </c>
       <c r="H67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>20</v>
@@ -15212,7 +15212,7 @@
         <v>19</v>
       </c>
       <c r="H68" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>20</v>
@@ -15262,7 +15262,7 @@
         <v>19</v>
       </c>
       <c r="H69" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>20</v>
@@ -15312,7 +15312,7 @@
         <v>19</v>
       </c>
       <c r="H70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>20</v>
@@ -15362,7 +15362,7 @@
         <v>19</v>
       </c>
       <c r="H71" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>20</v>
@@ -15412,7 +15412,7 @@
         <v>19</v>
       </c>
       <c r="H72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>20</v>
@@ -15462,7 +15462,7 @@
         <v>19</v>
       </c>
       <c r="H73" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>20</v>
@@ -15512,7 +15512,7 @@
         <v>19</v>
       </c>
       <c r="H74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>20</v>
@@ -15562,7 +15562,7 @@
         <v>19</v>
       </c>
       <c r="H75" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>20</v>
@@ -15612,7 +15612,7 @@
         <v>19</v>
       </c>
       <c r="H76" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>20</v>
@@ -15662,7 +15662,7 @@
         <v>19</v>
       </c>
       <c r="H77" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>20</v>
@@ -15712,7 +15712,7 @@
         <v>19</v>
       </c>
       <c r="H78" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>20</v>
@@ -15762,7 +15762,7 @@
         <v>19</v>
       </c>
       <c r="H79" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>20</v>
@@ -15812,7 +15812,7 @@
         <v>19</v>
       </c>
       <c r="H80" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>20</v>
@@ -15862,7 +15862,7 @@
         <v>19</v>
       </c>
       <c r="H81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>20</v>
@@ -15912,7 +15912,7 @@
         <v>19</v>
       </c>
       <c r="H82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>20</v>
@@ -15962,7 +15962,7 @@
         <v>19</v>
       </c>
       <c r="H83" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>20</v>
@@ -16012,7 +16012,7 @@
         <v>19</v>
       </c>
       <c r="H84" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>20</v>
@@ -16062,7 +16062,7 @@
         <v>19</v>
       </c>
       <c r="H85" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>20</v>
@@ -16112,7 +16112,7 @@
         <v>19</v>
       </c>
       <c r="H86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>20</v>
@@ -16162,7 +16162,7 @@
         <v>19</v>
       </c>
       <c r="H87" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>20</v>
@@ -16212,7 +16212,7 @@
         <v>19</v>
       </c>
       <c r="H88" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>20</v>
@@ -16262,7 +16262,7 @@
         <v>19</v>
       </c>
       <c r="H89" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>20</v>
@@ -16312,7 +16312,7 @@
         <v>19</v>
       </c>
       <c r="H90" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>20</v>
@@ -16362,7 +16362,7 @@
         <v>19</v>
       </c>
       <c r="H91" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>20</v>
@@ -16412,7 +16412,7 @@
         <v>19</v>
       </c>
       <c r="H92" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>20</v>
@@ -16462,7 +16462,7 @@
         <v>19</v>
       </c>
       <c r="H93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>20</v>
@@ -16512,7 +16512,7 @@
         <v>19</v>
       </c>
       <c r="H94" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>20</v>
@@ -16562,7 +16562,7 @@
         <v>19</v>
       </c>
       <c r="H95" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>20</v>
@@ -16612,7 +16612,7 @@
         <v>19</v>
       </c>
       <c r="H96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>20</v>
@@ -16662,7 +16662,7 @@
         <v>19</v>
       </c>
       <c r="H97" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>20</v>
@@ -16712,7 +16712,7 @@
         <v>19</v>
       </c>
       <c r="H98" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>20</v>
@@ -16762,7 +16762,7 @@
         <v>19</v>
       </c>
       <c r="H99" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>20</v>
@@ -16812,7 +16812,7 @@
         <v>19</v>
       </c>
       <c r="H100" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>20</v>
@@ -16862,7 +16862,7 @@
         <v>19</v>
       </c>
       <c r="H101" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>20</v>
@@ -16912,7 +16912,7 @@
         <v>19</v>
       </c>
       <c r="H102" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>20</v>
@@ -16962,7 +16962,7 @@
         <v>19</v>
       </c>
       <c r="H103" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>20</v>
@@ -17012,7 +17012,7 @@
         <v>19</v>
       </c>
       <c r="H104" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>20</v>
@@ -17062,7 +17062,7 @@
         <v>19</v>
       </c>
       <c r="H105" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>20</v>
@@ -17112,7 +17112,7 @@
         <v>19</v>
       </c>
       <c r="H106" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>20</v>
@@ -17162,7 +17162,7 @@
         <v>19</v>
       </c>
       <c r="H107" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>20</v>
@@ -17212,7 +17212,7 @@
         <v>19</v>
       </c>
       <c r="H108" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>20</v>
@@ -17262,7 +17262,7 @@
         <v>19</v>
       </c>
       <c r="H109" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>20</v>
@@ -17312,7 +17312,7 @@
         <v>19</v>
       </c>
       <c r="H110" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>20</v>
@@ -17362,7 +17362,7 @@
         <v>19</v>
       </c>
       <c r="H111" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>20</v>
@@ -17412,7 +17412,7 @@
         <v>19</v>
       </c>
       <c r="H112" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>20</v>
@@ -17462,7 +17462,7 @@
         <v>19</v>
       </c>
       <c r="H113" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>20</v>
@@ -17512,7 +17512,7 @@
         <v>19</v>
       </c>
       <c r="H114" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>20</v>
@@ -17562,7 +17562,7 @@
         <v>19</v>
       </c>
       <c r="H115" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>20</v>
@@ -17612,7 +17612,7 @@
         <v>19</v>
       </c>
       <c r="H116" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>20</v>
@@ -17662,7 +17662,7 @@
         <v>19</v>
       </c>
       <c r="H117" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>20</v>
@@ -17712,7 +17712,7 @@
         <v>19</v>
       </c>
       <c r="H118" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>20</v>
@@ -17762,7 +17762,7 @@
         <v>19</v>
       </c>
       <c r="H119" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>20</v>
@@ -17812,7 +17812,7 @@
         <v>19</v>
       </c>
       <c r="H120" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>20</v>
@@ -17862,7 +17862,7 @@
         <v>19</v>
       </c>
       <c r="H121" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>20</v>
@@ -17912,7 +17912,7 @@
         <v>19</v>
       </c>
       <c r="H122" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>20</v>
@@ -17962,7 +17962,7 @@
         <v>19</v>
       </c>
       <c r="H123" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>20</v>
@@ -18012,7 +18012,7 @@
         <v>19</v>
       </c>
       <c r="H124" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>20</v>
@@ -18062,7 +18062,7 @@
         <v>19</v>
       </c>
       <c r="H125" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>20</v>
@@ -18112,7 +18112,7 @@
         <v>19</v>
       </c>
       <c r="H126" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>20</v>
@@ -18162,7 +18162,7 @@
         <v>19</v>
       </c>
       <c r="H127" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>20</v>
@@ -18212,7 +18212,7 @@
         <v>19</v>
       </c>
       <c r="H128" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>20</v>
@@ -18262,7 +18262,7 @@
         <v>19</v>
       </c>
       <c r="H129" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>20</v>
@@ -18312,7 +18312,7 @@
         <v>19</v>
       </c>
       <c r="H130" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>20</v>
@@ -18361,8 +18361,8 @@
       <c r="G131" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H131" s="2">
-        <v>4</v>
+      <c r="H131" s="3">
+        <v>2</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>20</v>
@@ -18412,7 +18412,7 @@
         <v>19</v>
       </c>
       <c r="H132" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>20</v>
@@ -18462,7 +18462,7 @@
         <v>19</v>
       </c>
       <c r="H133" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>20</v>
@@ -18512,7 +18512,7 @@
         <v>19</v>
       </c>
       <c r="H134" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>20</v>
@@ -18562,7 +18562,7 @@
         <v>19</v>
       </c>
       <c r="H135" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>20</v>
@@ -18612,7 +18612,7 @@
         <v>19</v>
       </c>
       <c r="H136" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>20</v>
@@ -18662,7 +18662,7 @@
         <v>19</v>
       </c>
       <c r="H137" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>20</v>
@@ -18712,7 +18712,7 @@
         <v>19</v>
       </c>
       <c r="H138" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>20</v>
@@ -18762,7 +18762,7 @@
         <v>19</v>
       </c>
       <c r="H139" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>20</v>
@@ -18812,7 +18812,7 @@
         <v>19</v>
       </c>
       <c r="H140" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>20</v>
@@ -18862,7 +18862,7 @@
         <v>19</v>
       </c>
       <c r="H141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>20</v>
@@ -18912,7 +18912,7 @@
         <v>19</v>
       </c>
       <c r="H142" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>20</v>
@@ -18962,7 +18962,7 @@
         <v>19</v>
       </c>
       <c r="H143" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>20</v>
@@ -19012,7 +19012,7 @@
         <v>19</v>
       </c>
       <c r="H144" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>20</v>
@@ -19062,7 +19062,7 @@
         <v>19</v>
       </c>
       <c r="H145" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>20</v>
@@ -19112,7 +19112,7 @@
         <v>19</v>
       </c>
       <c r="H146" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>20</v>
@@ -19162,7 +19162,7 @@
         <v>19</v>
       </c>
       <c r="H147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I147" s="2" t="s">
         <v>20</v>
@@ -19212,7 +19212,7 @@
         <v>19</v>
       </c>
       <c r="H148" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>20</v>
@@ -19262,7 +19262,7 @@
         <v>19</v>
       </c>
       <c r="H149" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I149" s="2" t="s">
         <v>20</v>
@@ -19312,7 +19312,7 @@
         <v>19</v>
       </c>
       <c r="H150" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I150" s="2" t="s">
         <v>20</v>
@@ -19362,7 +19362,7 @@
         <v>19</v>
       </c>
       <c r="H151" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>20</v>
@@ -19412,7 +19412,7 @@
         <v>19</v>
       </c>
       <c r="H152" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>20</v>
@@ -19462,7 +19462,7 @@
         <v>19</v>
       </c>
       <c r="H153" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I153" s="2" t="s">
         <v>20</v>
@@ -19512,7 +19512,7 @@
         <v>19</v>
       </c>
       <c r="H154" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I154" s="2" t="s">
         <v>20</v>
@@ -19562,7 +19562,7 @@
         <v>19</v>
       </c>
       <c r="H155" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I155" s="2" t="s">
         <v>20</v>
@@ -19612,7 +19612,7 @@
         <v>19</v>
       </c>
       <c r="H156" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I156" s="2" t="s">
         <v>20</v>
@@ -19662,7 +19662,7 @@
         <v>19</v>
       </c>
       <c r="H157" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I157" s="2" t="s">
         <v>20</v>
@@ -19712,7 +19712,7 @@
         <v>19</v>
       </c>
       <c r="H158" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I158" s="2" t="s">
         <v>20</v>
@@ -19762,7 +19762,7 @@
         <v>19</v>
       </c>
       <c r="H159" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>20</v>
@@ -19812,7 +19812,7 @@
         <v>19</v>
       </c>
       <c r="H160" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I160" s="2" t="s">
         <v>20</v>
@@ -19862,7 +19862,7 @@
         <v>19</v>
       </c>
       <c r="H161" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I161" s="2" t="s">
         <v>20</v>
@@ -19912,7 +19912,7 @@
         <v>19</v>
       </c>
       <c r="H162" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I162" s="2" t="s">
         <v>20</v>
@@ -19962,7 +19962,7 @@
         <v>19</v>
       </c>
       <c r="H163" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I163" s="2" t="s">
         <v>20</v>
@@ -20012,7 +20012,7 @@
         <v>19</v>
       </c>
       <c r="H164" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I164" s="2" t="s">
         <v>20</v>
@@ -20062,7 +20062,7 @@
         <v>19</v>
       </c>
       <c r="H165" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I165" s="2" t="s">
         <v>20</v>
@@ -20112,7 +20112,7 @@
         <v>19</v>
       </c>
       <c r="H166" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I166" s="2" t="s">
         <v>20</v>
@@ -20162,7 +20162,7 @@
         <v>19</v>
       </c>
       <c r="H167" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I167" s="2" t="s">
         <v>20</v>
@@ -20212,7 +20212,7 @@
         <v>19</v>
       </c>
       <c r="H168" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I168" s="2" t="s">
         <v>20</v>
@@ -20262,7 +20262,7 @@
         <v>19</v>
       </c>
       <c r="H169" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I169" s="2" t="s">
         <v>20</v>
@@ -20312,7 +20312,7 @@
         <v>19</v>
       </c>
       <c r="H170" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I170" s="2" t="s">
         <v>20</v>
@@ -20362,7 +20362,7 @@
         <v>19</v>
       </c>
       <c r="H171" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I171" s="2" t="s">
         <v>20</v>
@@ -20412,7 +20412,7 @@
         <v>19</v>
       </c>
       <c r="H172" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I172" s="2" t="s">
         <v>20</v>
@@ -20462,7 +20462,7 @@
         <v>19</v>
       </c>
       <c r="H173" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I173" s="2" t="s">
         <v>20</v>
@@ -20512,7 +20512,7 @@
         <v>19</v>
       </c>
       <c r="H174" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I174" s="2" t="s">
         <v>20</v>
@@ -20562,7 +20562,7 @@
         <v>19</v>
       </c>
       <c r="H175" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I175" s="2" t="s">
         <v>20</v>
@@ -20612,7 +20612,7 @@
         <v>19</v>
       </c>
       <c r="H176" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I176" s="2" t="s">
         <v>20</v>
@@ -20662,7 +20662,7 @@
         <v>19</v>
       </c>
       <c r="H177" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I177" s="2" t="s">
         <v>20</v>
@@ -20712,7 +20712,7 @@
         <v>19</v>
       </c>
       <c r="H178" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I178" s="2" t="s">
         <v>20</v>
@@ -20762,7 +20762,7 @@
         <v>19</v>
       </c>
       <c r="H179" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I179" s="2" t="s">
         <v>20</v>
@@ -20812,7 +20812,7 @@
         <v>19</v>
       </c>
       <c r="H180" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I180" s="2" t="s">
         <v>20</v>
@@ -20862,7 +20862,7 @@
         <v>19</v>
       </c>
       <c r="H181" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I181" s="2" t="s">
         <v>20</v>
@@ -20912,7 +20912,7 @@
         <v>19</v>
       </c>
       <c r="H182" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I182" s="2" t="s">
         <v>20</v>
@@ -20962,7 +20962,7 @@
         <v>19</v>
       </c>
       <c r="H183" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I183" s="2" t="s">
         <v>20</v>
@@ -21012,7 +21012,7 @@
         <v>19</v>
       </c>
       <c r="H184" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I184" s="2" t="s">
         <v>20</v>
@@ -21062,7 +21062,7 @@
         <v>19</v>
       </c>
       <c r="H185" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I185" s="2" t="s">
         <v>20</v>
@@ -21112,7 +21112,7 @@
         <v>19</v>
       </c>
       <c r="H186" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I186" s="2" t="s">
         <v>20</v>
@@ -21162,7 +21162,7 @@
         <v>19</v>
       </c>
       <c r="H187" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I187" s="2" t="s">
         <v>20</v>
@@ -21212,7 +21212,7 @@
         <v>19</v>
       </c>
       <c r="H188" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I188" s="2" t="s">
         <v>20</v>
@@ -21262,7 +21262,7 @@
         <v>19</v>
       </c>
       <c r="H189" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I189" s="2" t="s">
         <v>20</v>
@@ -21312,7 +21312,7 @@
         <v>19</v>
       </c>
       <c r="H190" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I190" s="2" t="s">
         <v>20</v>
@@ -21362,7 +21362,7 @@
         <v>19</v>
       </c>
       <c r="H191" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I191" s="2" t="s">
         <v>20</v>
@@ -21412,7 +21412,7 @@
         <v>19</v>
       </c>
       <c r="H192" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I192" s="2" t="s">
         <v>20</v>
@@ -21462,7 +21462,7 @@
         <v>19</v>
       </c>
       <c r="H193" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I193" s="2" t="s">
         <v>20</v>
@@ -21512,7 +21512,7 @@
         <v>19</v>
       </c>
       <c r="H194" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I194" s="2" t="s">
         <v>20</v>
@@ -21562,7 +21562,7 @@
         <v>19</v>
       </c>
       <c r="H195" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I195" s="2" t="s">
         <v>20</v>
@@ -21612,7 +21612,7 @@
         <v>19</v>
       </c>
       <c r="H196" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I196" s="2" t="s">
         <v>20</v>
@@ -21662,7 +21662,7 @@
         <v>19</v>
       </c>
       <c r="H197" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I197" s="2" t="s">
         <v>20</v>
@@ -21712,7 +21712,7 @@
         <v>19</v>
       </c>
       <c r="H198" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I198" s="2" t="s">
         <v>20</v>
@@ -21762,7 +21762,7 @@
         <v>19</v>
       </c>
       <c r="H199" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I199" s="2" t="s">
         <v>20</v>
@@ -21812,7 +21812,7 @@
         <v>19</v>
       </c>
       <c r="H200" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I200" s="2" t="s">
         <v>20</v>
@@ -21862,7 +21862,7 @@
         <v>19</v>
       </c>
       <c r="H201" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I201" s="2" t="s">
         <v>20</v>
@@ -21912,7 +21912,7 @@
         <v>19</v>
       </c>
       <c r="H202" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I202" s="2" t="s">
         <v>20</v>
@@ -21962,7 +21962,7 @@
         <v>19</v>
       </c>
       <c r="H203" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I203" s="2" t="s">
         <v>20</v>
@@ -22012,7 +22012,7 @@
         <v>19</v>
       </c>
       <c r="H204" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I204" s="2" t="s">
         <v>20</v>
@@ -22062,7 +22062,7 @@
         <v>19</v>
       </c>
       <c r="H205" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I205" s="2" t="s">
         <v>20</v>
@@ -22112,7 +22112,7 @@
         <v>19</v>
       </c>
       <c r="H206" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I206" s="2" t="s">
         <v>20</v>
@@ -22162,7 +22162,7 @@
         <v>19</v>
       </c>
       <c r="H207" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I207" s="2" t="s">
         <v>20</v>
@@ -22212,7 +22212,7 @@
         <v>19</v>
       </c>
       <c r="H208" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I208" s="2" t="s">
         <v>20</v>
@@ -22262,7 +22262,7 @@
         <v>19</v>
       </c>
       <c r="H209" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I209" s="2" t="s">
         <v>20</v>
@@ -22312,7 +22312,7 @@
         <v>19</v>
       </c>
       <c r="H210" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I210" s="2" t="s">
         <v>20</v>
@@ -22362,7 +22362,7 @@
         <v>19</v>
       </c>
       <c r="H211" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I211" s="2" t="s">
         <v>20</v>
@@ -22412,7 +22412,7 @@
         <v>19</v>
       </c>
       <c r="H212" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I212" s="2" t="s">
         <v>20</v>
@@ -22462,7 +22462,7 @@
         <v>19</v>
       </c>
       <c r="H213" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I213" s="2" t="s">
         <v>20</v>
@@ -22512,7 +22512,7 @@
         <v>19</v>
       </c>
       <c r="H214" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I214" s="2" t="s">
         <v>20</v>
@@ -22562,7 +22562,7 @@
         <v>19</v>
       </c>
       <c r="H215" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I215" s="2" t="s">
         <v>20</v>
@@ -22612,7 +22612,7 @@
         <v>19</v>
       </c>
       <c r="H216" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I216" s="2" t="s">
         <v>20</v>
@@ -22662,7 +22662,7 @@
         <v>19</v>
       </c>
       <c r="H217" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I217" s="2" t="s">
         <v>20</v>
@@ -22712,7 +22712,7 @@
         <v>19</v>
       </c>
       <c r="H218" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I218" s="2" t="s">
         <v>20</v>
@@ -22762,7 +22762,7 @@
         <v>19</v>
       </c>
       <c r="H219" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I219" s="2" t="s">
         <v>20</v>
@@ -22812,7 +22812,7 @@
         <v>19</v>
       </c>
       <c r="H220" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I220" s="2" t="s">
         <v>20</v>
@@ -22862,7 +22862,7 @@
         <v>19</v>
       </c>
       <c r="H221" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I221" s="2" t="s">
         <v>20</v>
@@ -22912,7 +22912,7 @@
         <v>19</v>
       </c>
       <c r="H222" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I222" s="2" t="s">
         <v>20</v>
@@ -22962,7 +22962,7 @@
         <v>19</v>
       </c>
       <c r="H223" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I223" s="2" t="s">
         <v>20</v>
@@ -23012,7 +23012,7 @@
         <v>19</v>
       </c>
       <c r="H224" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I224" s="2" t="s">
         <v>20</v>
@@ -23062,7 +23062,7 @@
         <v>19</v>
       </c>
       <c r="H225" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I225" s="2" t="s">
         <v>20</v>
@@ -23112,7 +23112,7 @@
         <v>19</v>
       </c>
       <c r="H226" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I226" s="2" t="s">
         <v>20</v>
@@ -23162,7 +23162,7 @@
         <v>19</v>
       </c>
       <c r="H227" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I227" s="2" t="s">
         <v>20</v>
@@ -23212,7 +23212,7 @@
         <v>19</v>
       </c>
       <c r="H228" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I228" s="2" t="s">
         <v>20</v>
@@ -23262,7 +23262,7 @@
         <v>19</v>
       </c>
       <c r="H229" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I229" s="2" t="s">
         <v>20</v>
@@ -23312,7 +23312,7 @@
         <v>19</v>
       </c>
       <c r="H230" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I230" s="2" t="s">
         <v>20</v>
@@ -23362,7 +23362,7 @@
         <v>19</v>
       </c>
       <c r="H231" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I231" s="2" t="s">
         <v>20</v>
@@ -23412,7 +23412,7 @@
         <v>19</v>
       </c>
       <c r="H232" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I232" s="2" t="s">
         <v>20</v>
@@ -23462,7 +23462,7 @@
         <v>19</v>
       </c>
       <c r="H233" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I233" s="2" t="s">
         <v>20</v>
@@ -23512,7 +23512,7 @@
         <v>19</v>
       </c>
       <c r="H234" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I234" s="2" t="s">
         <v>20</v>
@@ -23562,7 +23562,7 @@
         <v>19</v>
       </c>
       <c r="H235" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I235" s="2" t="s">
         <v>20</v>
@@ -23612,7 +23612,7 @@
         <v>19</v>
       </c>
       <c r="H236" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I236" s="2" t="s">
         <v>20</v>
@@ -23662,7 +23662,7 @@
         <v>19</v>
       </c>
       <c r="H237" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I237" s="2" t="s">
         <v>20</v>
@@ -23712,7 +23712,7 @@
         <v>19</v>
       </c>
       <c r="H238" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I238" s="2" t="s">
         <v>20</v>
@@ -23762,7 +23762,7 @@
         <v>19</v>
       </c>
       <c r="H239" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I239" s="2" t="s">
         <v>20</v>
@@ -23812,7 +23812,7 @@
         <v>19</v>
       </c>
       <c r="H240" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I240" s="2" t="s">
         <v>20</v>
@@ -23862,7 +23862,7 @@
         <v>19</v>
       </c>
       <c r="H241" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I241" s="2" t="s">
         <v>20</v>
@@ -23912,7 +23912,7 @@
         <v>19</v>
       </c>
       <c r="H242" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I242" s="2" t="s">
         <v>20</v>
@@ -23962,7 +23962,7 @@
         <v>19</v>
       </c>
       <c r="H243" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I243" s="2" t="s">
         <v>20</v>
@@ -24012,7 +24012,7 @@
         <v>19</v>
       </c>
       <c r="H244" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I244" s="2" t="s">
         <v>20</v>
@@ -24062,7 +24062,7 @@
         <v>19</v>
       </c>
       <c r="H245" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I245" s="2" t="s">
         <v>20</v>
@@ -24112,7 +24112,7 @@
         <v>19</v>
       </c>
       <c r="H246" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I246" s="2" t="s">
         <v>20</v>
@@ -24162,7 +24162,7 @@
         <v>19</v>
       </c>
       <c r="H247" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I247" s="2" t="s">
         <v>20</v>
@@ -24212,7 +24212,7 @@
         <v>19</v>
       </c>
       <c r="H248" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I248" s="2" t="s">
         <v>20</v>
@@ -24262,7 +24262,7 @@
         <v>19</v>
       </c>
       <c r="H249" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I249" s="2" t="s">
         <v>20</v>
@@ -24312,7 +24312,7 @@
         <v>19</v>
       </c>
       <c r="H250" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I250" s="2" t="s">
         <v>20</v>
@@ -24362,7 +24362,7 @@
         <v>19</v>
       </c>
       <c r="H251" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I251" s="2" t="s">
         <v>20</v>
@@ -24412,7 +24412,7 @@
         <v>19</v>
       </c>
       <c r="H252" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I252" s="2" t="s">
         <v>20</v>
@@ -24462,7 +24462,7 @@
         <v>19</v>
       </c>
       <c r="H253" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I253" s="2" t="s">
         <v>20</v>
@@ -24512,7 +24512,7 @@
         <v>19</v>
       </c>
       <c r="H254" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I254" s="2" t="s">
         <v>20</v>
@@ -24562,7 +24562,7 @@
         <v>19</v>
       </c>
       <c r="H255" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I255" s="2" t="s">
         <v>20</v>
@@ -24612,7 +24612,7 @@
         <v>19</v>
       </c>
       <c r="H256" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I256" s="2" t="s">
         <v>20</v>
@@ -24662,7 +24662,7 @@
         <v>19</v>
       </c>
       <c r="H257" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I257" s="2" t="s">
         <v>20</v>
@@ -24712,7 +24712,7 @@
         <v>19</v>
       </c>
       <c r="H258" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I258" s="2" t="s">
         <v>20</v>
@@ -24762,7 +24762,7 @@
         <v>19</v>
       </c>
       <c r="H259" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I259" s="2" t="s">
         <v>20</v>
@@ -24812,7 +24812,7 @@
         <v>19</v>
       </c>
       <c r="H260" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I260" s="2" t="s">
         <v>20</v>
@@ -24862,7 +24862,7 @@
         <v>19</v>
       </c>
       <c r="H261" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I261" s="2" t="s">
         <v>20</v>
@@ -24912,7 +24912,7 @@
         <v>19</v>
       </c>
       <c r="H262" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I262" s="2" t="s">
         <v>20</v>
@@ -24962,7 +24962,7 @@
         <v>19</v>
       </c>
       <c r="H263" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I263" s="2" t="s">
         <v>20</v>
@@ -25012,7 +25012,7 @@
         <v>19</v>
       </c>
       <c r="H264" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I264" s="2" t="s">
         <v>20</v>
@@ -25062,7 +25062,7 @@
         <v>19</v>
       </c>
       <c r="H265" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I265" s="2" t="s">
         <v>20</v>
@@ -25112,7 +25112,7 @@
         <v>19</v>
       </c>
       <c r="H266" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I266" s="2" t="s">
         <v>20</v>
@@ -25162,7 +25162,7 @@
         <v>19</v>
       </c>
       <c r="H267" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I267" s="2" t="s">
         <v>20</v>
@@ -25212,7 +25212,7 @@
         <v>19</v>
       </c>
       <c r="H268" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I268" s="2" t="s">
         <v>20</v>
@@ -25262,7 +25262,7 @@
         <v>19</v>
       </c>
       <c r="H269" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I269" s="2" t="s">
         <v>20</v>
@@ -25312,7 +25312,7 @@
         <v>19</v>
       </c>
       <c r="H270" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I270" s="2" t="s">
         <v>20</v>
@@ -25362,7 +25362,7 @@
         <v>19</v>
       </c>
       <c r="H271" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I271" s="2" t="s">
         <v>20</v>
@@ -25412,7 +25412,7 @@
         <v>19</v>
       </c>
       <c r="H272" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I272" s="2" t="s">
         <v>20</v>
@@ -25462,7 +25462,7 @@
         <v>19</v>
       </c>
       <c r="H273" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I273" s="2" t="s">
         <v>20</v>
@@ -25512,7 +25512,7 @@
         <v>19</v>
       </c>
       <c r="H274" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I274" s="2" t="s">
         <v>20</v>
@@ -25562,7 +25562,7 @@
         <v>19</v>
       </c>
       <c r="H275" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I275" s="2" t="s">
         <v>20</v>
@@ -25612,7 +25612,7 @@
         <v>19</v>
       </c>
       <c r="H276" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I276" s="2" t="s">
         <v>20</v>
@@ -25662,7 +25662,7 @@
         <v>19</v>
       </c>
       <c r="H277" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I277" s="2" t="s">
         <v>20</v>
@@ -25712,7 +25712,7 @@
         <v>19</v>
       </c>
       <c r="H278" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I278" s="2" t="s">
         <v>20</v>
@@ -25762,7 +25762,7 @@
         <v>19</v>
       </c>
       <c r="H279" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I279" s="2" t="s">
         <v>20</v>
@@ -25812,7 +25812,7 @@
         <v>19</v>
       </c>
       <c r="H280" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I280" s="2" t="s">
         <v>20</v>
@@ -25862,7 +25862,7 @@
         <v>19</v>
       </c>
       <c r="H281" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I281" s="2" t="s">
         <v>20</v>
@@ -25912,7 +25912,7 @@
         <v>19</v>
       </c>
       <c r="H282" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I282" s="2" t="s">
         <v>20</v>
@@ -25962,7 +25962,7 @@
         <v>19</v>
       </c>
       <c r="H283" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I283" s="2" t="s">
         <v>20</v>
@@ -26012,7 +26012,7 @@
         <v>19</v>
       </c>
       <c r="H284" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I284" s="2" t="s">
         <v>20</v>
@@ -26062,7 +26062,7 @@
         <v>19</v>
       </c>
       <c r="H285" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I285" s="2" t="s">
         <v>20</v>
@@ -26112,7 +26112,7 @@
         <v>19</v>
       </c>
       <c r="H286" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I286" s="2" t="s">
         <v>20</v>
@@ -26162,7 +26162,7 @@
         <v>19</v>
       </c>
       <c r="H287" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I287" s="2" t="s">
         <v>20</v>
@@ -26812,7 +26812,7 @@
         <v>19</v>
       </c>
       <c r="H300" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I300" s="2" t="s">
         <v>20</v>
@@ -26862,7 +26862,7 @@
         <v>19</v>
       </c>
       <c r="H301" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I301" s="2" t="s">
         <v>20</v>
@@ -26912,7 +26912,7 @@
         <v>19</v>
       </c>
       <c r="H302" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I302" s="2" t="s">
         <v>20</v>
@@ -26962,7 +26962,7 @@
         <v>19</v>
       </c>
       <c r="H303" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I303" s="2" t="s">
         <v>20</v>
@@ -27012,7 +27012,7 @@
         <v>19</v>
       </c>
       <c r="H304" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I304" s="2" t="s">
         <v>20</v>
@@ -27062,7 +27062,7 @@
         <v>19</v>
       </c>
       <c r="H305" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I305" s="2" t="s">
         <v>20</v>
@@ -27112,7 +27112,7 @@
         <v>19</v>
       </c>
       <c r="H306" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I306" s="2" t="s">
         <v>20</v>
@@ -27162,7 +27162,7 @@
         <v>19</v>
       </c>
       <c r="H307" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I307" s="2" t="s">
         <v>20</v>
@@ -27212,7 +27212,7 @@
         <v>19</v>
       </c>
       <c r="H308" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I308" s="2" t="s">
         <v>20</v>
@@ -27262,7 +27262,7 @@
         <v>19</v>
       </c>
       <c r="H309" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I309" s="2" t="s">
         <v>20</v>
@@ -27312,7 +27312,7 @@
         <v>19</v>
       </c>
       <c r="H310" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I310" s="2" t="s">
         <v>20</v>
@@ -27362,7 +27362,7 @@
         <v>19</v>
       </c>
       <c r="H311" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I311" s="2" t="s">
         <v>20</v>
@@ -27412,7 +27412,7 @@
         <v>19</v>
       </c>
       <c r="H312" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I312" s="2" t="s">
         <v>20</v>
@@ -27462,7 +27462,7 @@
         <v>19</v>
       </c>
       <c r="H313" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I313" s="2" t="s">
         <v>20</v>
@@ -27512,7 +27512,7 @@
         <v>19</v>
       </c>
       <c r="H314" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I314" s="2" t="s">
         <v>20</v>
@@ -27562,7 +27562,7 @@
         <v>19</v>
       </c>
       <c r="H315" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I315" s="2" t="s">
         <v>20</v>
@@ -27612,7 +27612,7 @@
         <v>19</v>
       </c>
       <c r="H316" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I316" s="2" t="s">
         <v>20</v>
@@ -27662,7 +27662,7 @@
         <v>19</v>
       </c>
       <c r="H317" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I317" s="2" t="s">
         <v>20</v>
@@ -27786,7 +27786,7 @@
         <v>996</v>
       </c>
       <c r="H2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>20</v>
@@ -27836,7 +27836,7 @@
         <v>996</v>
       </c>
       <c r="H3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>20</v>
@@ -27886,7 +27886,7 @@
         <v>996</v>
       </c>
       <c r="H4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
@@ -27936,7 +27936,7 @@
         <v>996</v>
       </c>
       <c r="H5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -27986,7 +27986,7 @@
         <v>996</v>
       </c>
       <c r="H6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
@@ -28036,7 +28036,7 @@
         <v>996</v>
       </c>
       <c r="H7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>20</v>
@@ -28086,7 +28086,7 @@
         <v>996</v>
       </c>
       <c r="H8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>20</v>
@@ -28136,7 +28136,7 @@
         <v>996</v>
       </c>
       <c r="H9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>20</v>
@@ -28186,7 +28186,7 @@
         <v>996</v>
       </c>
       <c r="H10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>20</v>
@@ -28236,7 +28236,7 @@
         <v>996</v>
       </c>
       <c r="H11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>20</v>
@@ -28286,7 +28286,7 @@
         <v>996</v>
       </c>
       <c r="H12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>20</v>
@@ -28336,7 +28336,7 @@
         <v>996</v>
       </c>
       <c r="H13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>20</v>
@@ -28386,7 +28386,7 @@
         <v>996</v>
       </c>
       <c r="H14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>20</v>
@@ -28436,7 +28436,7 @@
         <v>996</v>
       </c>
       <c r="H15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>20</v>
@@ -28486,7 +28486,7 @@
         <v>996</v>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>20</v>
@@ -28536,7 +28536,7 @@
         <v>996</v>
       </c>
       <c r="H17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>20</v>
@@ -28586,7 +28586,7 @@
         <v>996</v>
       </c>
       <c r="H18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>20</v>
@@ -28636,7 +28636,7 @@
         <v>996</v>
       </c>
       <c r="H19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>20</v>
@@ -28686,7 +28686,7 @@
         <v>996</v>
       </c>
       <c r="H20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>20</v>
@@ -35792,7 +35792,7 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>1508</v>
@@ -35842,7 +35842,7 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="2">
-        <v>1501</v>
+        <v>1201</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>1512</v>
@@ -35892,7 +35892,7 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" s="2">
-        <v>1502</v>
+        <v>1202</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>1515</v>
@@ -35942,7 +35942,7 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="2">
-        <v>1503</v>
+        <v>1203</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>1518</v>
@@ -35992,7 +35992,7 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" s="2">
-        <v>1504</v>
+        <v>1204</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>1521</v>
@@ -36042,7 +36042,7 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="2">
-        <v>1505</v>
+        <v>1205</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>1524</v>
@@ -36092,7 +36092,7 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" s="2">
-        <v>1506</v>
+        <v>1206</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>1527</v>
@@ -36142,7 +36142,7 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="2">
-        <v>1507</v>
+        <v>1207</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>1530</v>
@@ -36192,7 +36192,7 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" s="2">
-        <v>1508</v>
+        <v>1208</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>1533</v>
@@ -36242,7 +36242,7 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="2">
-        <v>1509</v>
+        <v>1209</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>1537</v>
@@ -36292,7 +36292,7 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="2">
-        <v>1510</v>
+        <v>1210</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>1541</v>
@@ -36342,7 +36342,7 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="2">
-        <v>1511</v>
+        <v>1211</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>1544</v>
@@ -36392,7 +36392,7 @@
     </row>
     <row r="154" spans="1:16">
       <c r="A154" s="2">
-        <v>1512</v>
+        <v>1212</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>1547</v>
@@ -36442,7 +36442,7 @@
     </row>
     <row r="155" spans="1:16">
       <c r="A155" s="2">
-        <v>1513</v>
+        <v>1213</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>1550</v>
@@ -36492,7 +36492,7 @@
     </row>
     <row r="156" spans="1:16">
       <c r="A156" s="2">
-        <v>1514</v>
+        <v>1214</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>1553</v>
@@ -36542,7 +36542,7 @@
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="2">
-        <v>1515</v>
+        <v>1215</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>1556</v>
@@ -36592,7 +36592,7 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" s="2">
-        <v>1516</v>
+        <v>1216</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>1559</v>
@@ -36642,7 +36642,7 @@
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="2">
-        <v>1517</v>
+        <v>1217</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>1562</v>
@@ -36692,7 +36692,7 @@
     </row>
     <row r="160" spans="1:16">
       <c r="A160" s="2">
-        <v>1518</v>
+        <v>1218</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>1565</v>
@@ -36742,7 +36742,7 @@
     </row>
     <row r="161" spans="1:16">
       <c r="A161" s="2">
-        <v>1519</v>
+        <v>1219</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>1568</v>
@@ -36792,7 +36792,7 @@
     </row>
     <row r="162" spans="1:16">
       <c r="A162" s="2">
-        <v>1520</v>
+        <v>1220</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>1571</v>
@@ -36842,7 +36842,7 @@
     </row>
     <row r="163" spans="1:16">
       <c r="A163" s="2">
-        <v>1521</v>
+        <v>1221</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>1574</v>
@@ -36892,7 +36892,7 @@
     </row>
     <row r="164" spans="1:16">
       <c r="A164" s="2">
-        <v>1522</v>
+        <v>1222</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>1577</v>
@@ -36942,7 +36942,7 @@
     </row>
     <row r="165" spans="1:16">
       <c r="A165" s="2">
-        <v>1523</v>
+        <v>1223</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>1580</v>
@@ -36992,7 +36992,7 @@
     </row>
     <row r="166" spans="1:16">
       <c r="A166" s="2">
-        <v>1524</v>
+        <v>1224</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>1583</v>
@@ -37042,7 +37042,7 @@
     </row>
     <row r="167" spans="1:16">
       <c r="A167" s="2">
-        <v>1525</v>
+        <v>1225</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>1586</v>
@@ -37092,7 +37092,7 @@
     </row>
     <row r="168" spans="1:16">
       <c r="A168" s="2">
-        <v>1526</v>
+        <v>1226</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>1589</v>
@@ -37142,7 +37142,7 @@
     </row>
     <row r="169" spans="1:16">
       <c r="A169" s="2">
-        <v>1527</v>
+        <v>1227</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>1592</v>
@@ -37192,7 +37192,7 @@
     </row>
     <row r="170" spans="1:16">
       <c r="A170" s="2">
-        <v>1528</v>
+        <v>1228</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>1595</v>
@@ -37242,7 +37242,7 @@
     </row>
     <row r="171" spans="1:16">
       <c r="A171" s="2">
-        <v>1529</v>
+        <v>1229</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>1598</v>
@@ -37292,7 +37292,7 @@
     </row>
     <row r="172" spans="1:16">
       <c r="A172" s="2">
-        <v>1530</v>
+        <v>1230</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>1601</v>
@@ -37342,7 +37342,7 @@
     </row>
     <row r="173" spans="1:16">
       <c r="A173" s="2">
-        <v>1531</v>
+        <v>1231</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>1604</v>
@@ -37392,7 +37392,7 @@
     </row>
     <row r="174" spans="1:16">
       <c r="A174" s="2">
-        <v>1532</v>
+        <v>1232</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>1607</v>
@@ -37442,7 +37442,7 @@
     </row>
     <row r="175" spans="1:16">
       <c r="A175" s="2">
-        <v>1533</v>
+        <v>1233</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>1610</v>
@@ -37492,7 +37492,7 @@
     </row>
     <row r="176" spans="1:16">
       <c r="A176" s="2">
-        <v>1534</v>
+        <v>1234</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>1613</v>
@@ -37542,7 +37542,7 @@
     </row>
     <row r="177" spans="1:16">
       <c r="A177" s="2">
-        <v>1535</v>
+        <v>1235</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>1616</v>
@@ -37592,7 +37592,7 @@
     </row>
     <row r="178" spans="1:16">
       <c r="A178" s="2">
-        <v>1536</v>
+        <v>1236</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>1619</v>
@@ -37642,7 +37642,7 @@
     </row>
     <row r="179" spans="1:16">
       <c r="A179" s="2">
-        <v>1537</v>
+        <v>1237</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>1622</v>
@@ -37692,7 +37692,7 @@
     </row>
     <row r="180" spans="1:16">
       <c r="A180" s="2">
-        <v>1538</v>
+        <v>1238</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>1625</v>
@@ -37742,7 +37742,7 @@
     </row>
     <row r="181" spans="1:16">
       <c r="A181" s="2">
-        <v>1539</v>
+        <v>1239</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>1628</v>
@@ -37792,7 +37792,7 @@
     </row>
     <row r="182" spans="1:16">
       <c r="A182" s="2">
-        <v>1540</v>
+        <v>1240</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>1631</v>
@@ -37842,7 +37842,7 @@
     </row>
     <row r="183" spans="1:16">
       <c r="A183" s="2">
-        <v>1541</v>
+        <v>1241</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>1634</v>
@@ -37892,7 +37892,7 @@
     </row>
     <row r="184" spans="1:16">
       <c r="A184" s="2">
-        <v>1542</v>
+        <v>1242</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>1637</v>
@@ -37942,7 +37942,7 @@
     </row>
     <row r="185" spans="1:16">
       <c r="A185" s="2">
-        <v>1543</v>
+        <v>1243</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>1640</v>
@@ -37992,7 +37992,7 @@
     </row>
     <row r="186" spans="1:16">
       <c r="A186" s="2">
-        <v>1544</v>
+        <v>1244</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>1643</v>
@@ -38042,7 +38042,7 @@
     </row>
     <row r="187" spans="1:16">
       <c r="A187" s="2">
-        <v>1545</v>
+        <v>1245</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>1646</v>
@@ -38092,7 +38092,7 @@
     </row>
     <row r="188" spans="1:16">
       <c r="A188" s="2">
-        <v>1546</v>
+        <v>1246</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>1649</v>
@@ -38142,7 +38142,7 @@
     </row>
     <row r="189" spans="1:16">
       <c r="A189" s="2">
-        <v>1547</v>
+        <v>1247</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>1652</v>
@@ -38192,7 +38192,7 @@
     </row>
     <row r="190" spans="1:16">
       <c r="A190" s="2">
-        <v>1548</v>
+        <v>1248</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>1655</v>
@@ -38242,7 +38242,7 @@
     </row>
     <row r="191" spans="1:16">
       <c r="A191" s="2">
-        <v>1549</v>
+        <v>1249</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>1658</v>
@@ -38292,7 +38292,7 @@
     </row>
     <row r="192" spans="1:16">
       <c r="A192" s="2">
-        <v>1550</v>
+        <v>1250</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>1661</v>
@@ -38342,7 +38342,7 @@
     </row>
     <row r="193" spans="1:16">
       <c r="A193" s="2">
-        <v>1551</v>
+        <v>1251</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>1664</v>
@@ -38392,7 +38392,7 @@
     </row>
     <row r="194" spans="1:16">
       <c r="A194" s="2">
-        <v>1552</v>
+        <v>1252</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>1667</v>
@@ -38442,7 +38442,7 @@
     </row>
     <row r="195" spans="1:16">
       <c r="A195" s="2">
-        <v>1553</v>
+        <v>1253</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>1670</v>
@@ -38492,7 +38492,7 @@
     </row>
     <row r="196" spans="1:16">
       <c r="A196" s="2">
-        <v>1554</v>
+        <v>1254</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>1673</v>
@@ -38542,7 +38542,7 @@
     </row>
     <row r="197" spans="1:16">
       <c r="A197" s="2">
-        <v>1555</v>
+        <v>1255</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>1676</v>
@@ -38592,7 +38592,7 @@
     </row>
     <row r="198" spans="1:16">
       <c r="A198" s="2">
-        <v>1556</v>
+        <v>1256</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>1679</v>
@@ -38642,7 +38642,7 @@
     </row>
     <row r="199" spans="1:16">
       <c r="A199" s="2">
-        <v>1557</v>
+        <v>1257</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>1682</v>
@@ -38692,7 +38692,7 @@
     </row>
     <row r="200" spans="1:16">
       <c r="A200" s="2">
-        <v>1558</v>
+        <v>1258</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>1685</v>
@@ -38742,7 +38742,7 @@
     </row>
     <row r="201" spans="1:16">
       <c r="A201" s="2">
-        <v>1559</v>
+        <v>1259</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>1688</v>
@@ -38792,7 +38792,7 @@
     </row>
     <row r="202" spans="1:16">
       <c r="A202" s="2">
-        <v>1560</v>
+        <v>1260</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>1691</v>
@@ -38842,7 +38842,7 @@
     </row>
     <row r="203" spans="1:16">
       <c r="A203" s="2">
-        <v>1561</v>
+        <v>1261</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>1694</v>
@@ -38892,7 +38892,7 @@
     </row>
     <row r="204" spans="1:16">
       <c r="A204" s="2">
-        <v>1562</v>
+        <v>1262</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>1697</v>
@@ -38942,7 +38942,7 @@
     </row>
     <row r="205" spans="1:16">
       <c r="A205" s="2">
-        <v>1563</v>
+        <v>1263</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>1700</v>
@@ -38992,7 +38992,7 @@
     </row>
     <row r="206" spans="1:16">
       <c r="A206" s="2">
-        <v>1564</v>
+        <v>1264</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>1703</v>
@@ -39042,7 +39042,7 @@
     </row>
     <row r="207" spans="1:16">
       <c r="A207" s="2">
-        <v>1565</v>
+        <v>1265</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>1706</v>
@@ -39092,7 +39092,7 @@
     </row>
     <row r="208" spans="1:16">
       <c r="A208" s="2">
-        <v>1566</v>
+        <v>1266</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>1709</v>
@@ -39142,7 +39142,7 @@
     </row>
     <row r="209" spans="1:16">
       <c r="A209" s="2">
-        <v>1567</v>
+        <v>1267</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>1712</v>
@@ -39192,7 +39192,7 @@
     </row>
     <row r="210" spans="1:16">
       <c r="A210" s="2">
-        <v>1568</v>
+        <v>1268</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>1715</v>
@@ -39242,7 +39242,7 @@
     </row>
     <row r="211" spans="1:16">
       <c r="A211" s="2">
-        <v>1569</v>
+        <v>1269</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>1718</v>
@@ -39292,7 +39292,7 @@
     </row>
     <row r="212" spans="1:16">
       <c r="A212" s="2">
-        <v>1570</v>
+        <v>1270</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>1721</v>
@@ -39342,7 +39342,7 @@
     </row>
     <row r="213" spans="1:16">
       <c r="A213" s="2">
-        <v>1571</v>
+        <v>1271</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>1724</v>
@@ -39392,7 +39392,7 @@
     </row>
     <row r="214" spans="1:16">
       <c r="A214" s="2">
-        <v>1572</v>
+        <v>1272</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>1727</v>
@@ -39442,7 +39442,7 @@
     </row>
     <row r="215" spans="1:16">
       <c r="A215" s="2">
-        <v>1573</v>
+        <v>1273</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>1730</v>
@@ -39492,7 +39492,7 @@
     </row>
     <row r="216" spans="1:16">
       <c r="A216" s="2">
-        <v>1574</v>
+        <v>1274</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>1733</v>
@@ -39542,7 +39542,7 @@
     </row>
     <row r="217" spans="1:16">
       <c r="A217" s="2">
-        <v>1575</v>
+        <v>1275</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>1736</v>
@@ -39592,7 +39592,7 @@
     </row>
     <row r="218" spans="1:16">
       <c r="A218" s="2">
-        <v>1576</v>
+        <v>1276</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>1739</v>
@@ -39642,7 +39642,7 @@
     </row>
     <row r="219" spans="1:16">
       <c r="A219" s="2">
-        <v>1577</v>
+        <v>1277</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>1742</v>
@@ -39692,7 +39692,7 @@
     </row>
     <row r="220" spans="1:16">
       <c r="A220" s="2">
-        <v>1578</v>
+        <v>1278</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>1745</v>
@@ -39742,7 +39742,7 @@
     </row>
     <row r="221" spans="1:16">
       <c r="A221" s="2">
-        <v>1579</v>
+        <v>1279</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>1748</v>
@@ -39792,7 +39792,7 @@
     </row>
     <row r="222" spans="1:16">
       <c r="A222" s="2">
-        <v>1580</v>
+        <v>1280</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>1751</v>
@@ -39842,7 +39842,7 @@
     </row>
     <row r="223" spans="1:16">
       <c r="A223" s="2">
-        <v>1581</v>
+        <v>1281</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>1754</v>
@@ -39892,7 +39892,7 @@
     </row>
     <row r="224" spans="1:16">
       <c r="A224" s="2">
-        <v>1582</v>
+        <v>1282</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>1757</v>
@@ -39942,7 +39942,7 @@
     </row>
     <row r="225" spans="1:16">
       <c r="A225" s="2">
-        <v>1583</v>
+        <v>1283</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>1760</v>
@@ -39992,7 +39992,7 @@
     </row>
     <row r="226" spans="1:16">
       <c r="A226" s="2">
-        <v>1584</v>
+        <v>1284</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>1763</v>
@@ -40042,7 +40042,7 @@
     </row>
     <row r="227" spans="1:16">
       <c r="A227" s="2">
-        <v>1585</v>
+        <v>1285</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>1766</v>
@@ -40092,7 +40092,7 @@
     </row>
     <row r="228" spans="1:16">
       <c r="A228" s="2">
-        <v>1586</v>
+        <v>1286</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>1769</v>
@@ -40142,7 +40142,7 @@
     </row>
     <row r="229" spans="1:16">
       <c r="A229" s="2">
-        <v>1587</v>
+        <v>1287</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>1772</v>
@@ -40192,7 +40192,7 @@
     </row>
     <row r="230" spans="1:16">
       <c r="A230" s="2">
-        <v>1588</v>
+        <v>1288</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>1775</v>
@@ -40242,7 +40242,7 @@
     </row>
     <row r="231" spans="1:16">
       <c r="A231" s="2">
-        <v>1589</v>
+        <v>1289</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>1778</v>
@@ -40292,7 +40292,7 @@
     </row>
     <row r="232" spans="1:16">
       <c r="A232" s="2">
-        <v>1590</v>
+        <v>1290</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>1781</v>
@@ -40342,7 +40342,7 @@
     </row>
     <row r="233" spans="1:16">
       <c r="A233" s="2">
-        <v>1591</v>
+        <v>1291</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>1784</v>
@@ -40392,7 +40392,7 @@
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="2">
-        <v>1592</v>
+        <v>1292</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>1787</v>
@@ -40442,7 +40442,7 @@
     </row>
     <row r="235" spans="1:16">
       <c r="A235" s="2">
-        <v>1593</v>
+        <v>1293</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>1790</v>
@@ -40492,7 +40492,7 @@
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="2">
-        <v>1594</v>
+        <v>1294</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>1793</v>
@@ -40542,7 +40542,7 @@
     </row>
     <row r="237" spans="1:16">
       <c r="A237" s="2">
-        <v>1595</v>
+        <v>1295</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>1796</v>
@@ -40592,7 +40592,7 @@
     </row>
     <row r="238" spans="1:16">
       <c r="A238" s="2">
-        <v>1596</v>
+        <v>1296</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>1799</v>
@@ -40642,7 +40642,7 @@
     </row>
     <row r="239" spans="1:16">
       <c r="A239" s="2">
-        <v>1597</v>
+        <v>1297</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>1802</v>
@@ -40692,7 +40692,7 @@
     </row>
     <row r="240" spans="1:16">
       <c r="A240" s="2">
-        <v>1598</v>
+        <v>1298</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>1805</v>
@@ -40742,7 +40742,7 @@
     </row>
     <row r="241" spans="1:16">
       <c r="A241" s="2">
-        <v>1599</v>
+        <v>1299</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>1808</v>
@@ -40792,7 +40792,7 @@
     </row>
     <row r="242" spans="1:16">
       <c r="A242" s="2">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>1811</v>
@@ -40842,7 +40842,7 @@
     </row>
     <row r="243" spans="1:16">
       <c r="A243" s="2">
-        <v>1601</v>
+        <v>1301</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>1814</v>
@@ -40892,7 +40892,7 @@
     </row>
     <row r="244" spans="1:16">
       <c r="A244" s="2">
-        <v>1602</v>
+        <v>1302</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>1817</v>
@@ -40942,7 +40942,7 @@
     </row>
     <row r="245" spans="1:16">
       <c r="A245" s="2">
-        <v>1603</v>
+        <v>1303</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>1820</v>
@@ -40992,7 +40992,7 @@
     </row>
     <row r="246" spans="1:16">
       <c r="A246" s="2">
-        <v>1604</v>
+        <v>1304</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>1823</v>
@@ -41042,7 +41042,7 @@
     </row>
     <row r="247" spans="1:16">
       <c r="A247" s="2">
-        <v>1605</v>
+        <v>1305</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>1826</v>
@@ -41092,7 +41092,7 @@
     </row>
     <row r="248" spans="1:16">
       <c r="A248" s="2">
-        <v>1606</v>
+        <v>1306</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>1829</v>
@@ -41142,7 +41142,7 @@
     </row>
     <row r="249" spans="1:16">
       <c r="A249" s="2">
-        <v>1607</v>
+        <v>1307</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>1832</v>
@@ -41192,7 +41192,7 @@
     </row>
     <row r="250" spans="1:16">
       <c r="A250" s="2">
-        <v>1608</v>
+        <v>1308</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>1835</v>
@@ -41242,7 +41242,7 @@
     </row>
     <row r="251" spans="1:16">
       <c r="A251" s="2">
-        <v>1609</v>
+        <v>1309</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>1838</v>
@@ -41292,7 +41292,7 @@
     </row>
     <row r="252" spans="1:16">
       <c r="A252" s="2">
-        <v>1610</v>
+        <v>1310</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>1841</v>
@@ -41342,7 +41342,7 @@
     </row>
     <row r="253" spans="1:16">
       <c r="A253" s="2">
-        <v>1611</v>
+        <v>1311</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>1844</v>
@@ -41392,7 +41392,7 @@
     </row>
     <row r="254" spans="1:16">
       <c r="A254" s="2">
-        <v>1612</v>
+        <v>1312</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>1847</v>
@@ -41442,7 +41442,7 @@
     </row>
     <row r="255" spans="1:16">
       <c r="A255" s="2">
-        <v>1613</v>
+        <v>1313</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>1851</v>
@@ -41492,7 +41492,7 @@
     </row>
     <row r="256" spans="1:16">
       <c r="A256" s="2">
-        <v>1614</v>
+        <v>1314</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>1855</v>
@@ -41542,7 +41542,7 @@
     </row>
     <row r="257" spans="1:16">
       <c r="A257" s="2">
-        <v>1615</v>
+        <v>1315</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>1859</v>
@@ -41592,7 +41592,7 @@
     </row>
     <row r="258" spans="1:16">
       <c r="A258" s="2">
-        <v>1616</v>
+        <v>1316</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>1862</v>
@@ -41642,7 +41642,7 @@
     </row>
     <row r="259" spans="1:16">
       <c r="A259" s="2">
-        <v>1617</v>
+        <v>1317</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>1865</v>
@@ -41692,7 +41692,7 @@
     </row>
     <row r="260" spans="1:16">
       <c r="A260" s="2">
-        <v>1618</v>
+        <v>1318</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>1868</v>
@@ -41742,7 +41742,7 @@
     </row>
     <row r="261" spans="1:16">
       <c r="A261" s="2">
-        <v>1619</v>
+        <v>1319</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>1871</v>
@@ -41792,7 +41792,7 @@
     </row>
     <row r="262" spans="1:16">
       <c r="A262" s="2">
-        <v>1620</v>
+        <v>1320</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>1874</v>
@@ -41842,7 +41842,7 @@
     </row>
     <row r="263" spans="1:16">
       <c r="A263" s="2">
-        <v>1621</v>
+        <v>1321</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>1877</v>
@@ -41892,7 +41892,7 @@
     </row>
     <row r="264" spans="1:16">
       <c r="A264" s="2">
-        <v>1622</v>
+        <v>1322</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>1880</v>
@@ -41942,7 +41942,7 @@
     </row>
     <row r="265" spans="1:16">
       <c r="A265" s="2">
-        <v>1623</v>
+        <v>1323</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>1883</v>
@@ -41992,7 +41992,7 @@
     </row>
     <row r="266" spans="1:16">
       <c r="A266" s="2">
-        <v>1624</v>
+        <v>1324</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>1886</v>
@@ -42042,7 +42042,7 @@
     </row>
     <row r="267" spans="1:16">
       <c r="A267" s="2">
-        <v>1625</v>
+        <v>1325</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>1889</v>
@@ -42092,7 +42092,7 @@
     </row>
     <row r="268" spans="1:16">
       <c r="A268" s="2">
-        <v>1626</v>
+        <v>1326</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>1892</v>
@@ -42142,7 +42142,7 @@
     </row>
     <row r="269" spans="1:16">
       <c r="A269" s="2">
-        <v>1627</v>
+        <v>1327</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>1895</v>
@@ -42192,7 +42192,7 @@
     </row>
     <row r="270" spans="1:16">
       <c r="A270" s="2">
-        <v>1628</v>
+        <v>1328</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>1898</v>
@@ -42242,7 +42242,7 @@
     </row>
     <row r="271" spans="1:16">
       <c r="A271" s="2">
-        <v>1629</v>
+        <v>1329</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>1901</v>
@@ -42292,7 +42292,7 @@
     </row>
     <row r="272" spans="1:16">
       <c r="A272" s="2">
-        <v>1630</v>
+        <v>1330</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>1904</v>
@@ -42342,7 +42342,7 @@
     </row>
     <row r="273" spans="1:16">
       <c r="A273" s="2">
-        <v>1631</v>
+        <v>1331</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>1907</v>
@@ -42392,7 +42392,7 @@
     </row>
     <row r="274" spans="1:16">
       <c r="A274" s="2">
-        <v>1632</v>
+        <v>1332</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>1910</v>
@@ -42442,7 +42442,7 @@
     </row>
     <row r="275" spans="1:16">
       <c r="A275" s="2">
-        <v>1633</v>
+        <v>1333</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>1913</v>
@@ -42492,7 +42492,7 @@
     </row>
     <row r="276" spans="1:16">
       <c r="A276" s="2">
-        <v>1634</v>
+        <v>1334</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>1916</v>
@@ -42542,7 +42542,7 @@
     </row>
     <row r="277" spans="1:16">
       <c r="A277" s="2">
-        <v>1635</v>
+        <v>1335</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>1919</v>
@@ -42592,7 +42592,7 @@
     </row>
     <row r="278" spans="1:16">
       <c r="A278" s="2">
-        <v>1636</v>
+        <v>1336</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>1922</v>
@@ -42642,7 +42642,7 @@
     </row>
     <row r="279" spans="1:16">
       <c r="A279" s="2">
-        <v>1637</v>
+        <v>1337</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>1925</v>
@@ -42692,7 +42692,7 @@
     </row>
     <row r="280" spans="1:16">
       <c r="A280" s="2">
-        <v>1638</v>
+        <v>1338</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>1928</v>
@@ -42742,7 +42742,7 @@
     </row>
     <row r="281" spans="1:16">
       <c r="A281" s="2">
-        <v>1639</v>
+        <v>1339</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>1931</v>
@@ -42792,7 +42792,7 @@
     </row>
     <row r="282" spans="1:16">
       <c r="A282" s="2">
-        <v>1640</v>
+        <v>1340</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>1934</v>
@@ -42842,7 +42842,7 @@
     </row>
     <row r="283" spans="1:16">
       <c r="A283" s="2">
-        <v>1641</v>
+        <v>1341</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>1937</v>
@@ -42892,7 +42892,7 @@
     </row>
     <row r="284" spans="1:16">
       <c r="A284" s="2">
-        <v>1642</v>
+        <v>1342</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>1940</v>
@@ -42942,7 +42942,7 @@
     </row>
     <row r="285" spans="1:16">
       <c r="A285" s="2">
-        <v>1643</v>
+        <v>1343</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>1943</v>
@@ -42992,7 +42992,7 @@
     </row>
     <row r="286" spans="1:16">
       <c r="A286" s="2">
-        <v>1644</v>
+        <v>1344</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>1946</v>
@@ -43042,7 +43042,7 @@
     </row>
     <row r="287" spans="1:16">
       <c r="A287" s="2">
-        <v>1645</v>
+        <v>1345</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>1949</v>
@@ -43092,7 +43092,7 @@
     </row>
     <row r="288" spans="1:16">
       <c r="A288" s="2">
-        <v>1646</v>
+        <v>1346</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>1952</v>
@@ -43142,7 +43142,7 @@
     </row>
     <row r="289" spans="1:16">
       <c r="A289" s="2">
-        <v>1647</v>
+        <v>1347</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>1955</v>
@@ -43192,7 +43192,7 @@
     </row>
     <row r="290" spans="1:16">
       <c r="A290" s="2">
-        <v>1648</v>
+        <v>1348</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>1958</v>
@@ -43242,7 +43242,7 @@
     </row>
     <row r="291" spans="1:16">
       <c r="A291" s="2">
-        <v>1649</v>
+        <v>1349</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>1961</v>
@@ -43292,7 +43292,7 @@
     </row>
     <row r="292" spans="1:16">
       <c r="A292" s="2">
-        <v>1650</v>
+        <v>1350</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>1964</v>
@@ -43342,7 +43342,7 @@
     </row>
     <row r="293" spans="1:16">
       <c r="A293" s="2">
-        <v>1651</v>
+        <v>1351</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>1967</v>
@@ -43392,7 +43392,7 @@
     </row>
     <row r="294" spans="1:16">
       <c r="A294" s="2">
-        <v>1652</v>
+        <v>1352</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>1970</v>
@@ -43442,7 +43442,7 @@
     </row>
     <row r="295" spans="1:16">
       <c r="A295" s="2">
-        <v>1653</v>
+        <v>1353</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>1973</v>
@@ -43492,7 +43492,7 @@
     </row>
     <row r="296" spans="1:16">
       <c r="A296" s="2">
-        <v>1654</v>
+        <v>1354</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>1976</v>
@@ -43542,7 +43542,7 @@
     </row>
     <row r="297" spans="1:16">
       <c r="A297" s="2">
-        <v>1655</v>
+        <v>1355</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>1979</v>
@@ -43592,7 +43592,7 @@
     </row>
     <row r="298" spans="1:16">
       <c r="A298" s="2">
-        <v>1656</v>
+        <v>1356</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>1982</v>
@@ -43642,7 +43642,7 @@
     </row>
     <row r="299" spans="1:16">
       <c r="A299" s="2">
-        <v>1657</v>
+        <v>1357</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>1985</v>
@@ -43692,7 +43692,7 @@
     </row>
     <row r="300" spans="1:16">
       <c r="A300" s="2">
-        <v>1658</v>
+        <v>1358</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>1988</v>
@@ -43742,7 +43742,7 @@
     </row>
     <row r="301" spans="1:16">
       <c r="A301" s="2">
-        <v>1659</v>
+        <v>1359</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>1991</v>
@@ -43792,7 +43792,7 @@
     </row>
     <row r="302" spans="1:16">
       <c r="A302" s="2">
-        <v>1660</v>
+        <v>1360</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>1994</v>
@@ -43842,7 +43842,7 @@
     </row>
     <row r="303" spans="1:16">
       <c r="A303" s="2">
-        <v>1661</v>
+        <v>1361</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>1997</v>
@@ -43892,7 +43892,7 @@
     </row>
     <row r="304" spans="1:16">
       <c r="A304" s="2">
-        <v>1662</v>
+        <v>1362</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>2000</v>
@@ -43942,7 +43942,7 @@
     </row>
     <row r="305" spans="1:16">
       <c r="A305" s="2">
-        <v>1663</v>
+        <v>1363</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>2003</v>
@@ -43992,7 +43992,7 @@
     </row>
     <row r="306" spans="1:16">
       <c r="A306" s="2">
-        <v>1664</v>
+        <v>1364</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>2006</v>
@@ -44042,7 +44042,7 @@
     </row>
     <row r="307" spans="1:16">
       <c r="A307" s="2">
-        <v>1665</v>
+        <v>1365</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>2009</v>
@@ -44092,7 +44092,7 @@
     </row>
     <row r="308" spans="1:16">
       <c r="A308" s="2">
-        <v>1666</v>
+        <v>1366</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>2012</v>
@@ -44142,7 +44142,7 @@
     </row>
     <row r="309" spans="1:16">
       <c r="A309" s="2">
-        <v>1667</v>
+        <v>1367</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>2015</v>
@@ -44192,7 +44192,7 @@
     </row>
     <row r="310" spans="1:16">
       <c r="A310" s="2">
-        <v>1668</v>
+        <v>1368</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>2018</v>
@@ -44242,7 +44242,7 @@
     </row>
     <row r="311" spans="1:16">
       <c r="A311" s="2">
-        <v>1669</v>
+        <v>1369</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>2021</v>
@@ -44292,7 +44292,7 @@
     </row>
     <row r="312" spans="1:16">
       <c r="A312" s="2">
-        <v>1670</v>
+        <v>1370</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>2024</v>
@@ -44342,7 +44342,7 @@
     </row>
     <row r="313" spans="1:16">
       <c r="A313" s="2">
-        <v>1671</v>
+        <v>1371</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>2027</v>
@@ -44392,7 +44392,7 @@
     </row>
     <row r="314" spans="1:16">
       <c r="A314" s="2">
-        <v>1672</v>
+        <v>1372</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>2030</v>
@@ -44442,7 +44442,7 @@
     </row>
     <row r="315" spans="1:16">
       <c r="A315" s="2">
-        <v>1673</v>
+        <v>1373</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>2033</v>
@@ -44492,7 +44492,7 @@
     </row>
     <row r="316" spans="1:16">
       <c r="A316" s="2">
-        <v>1674</v>
+        <v>1374</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>2036</v>
@@ -44542,7 +44542,7 @@
     </row>
     <row r="317" spans="1:16">
       <c r="A317" s="2">
-        <v>1675</v>
+        <v>1375</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>2039</v>
@@ -44592,7 +44592,7 @@
     </row>
     <row r="318" spans="1:16">
       <c r="A318" s="2">
-        <v>1676</v>
+        <v>1376</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>2042</v>
@@ -44642,7 +44642,7 @@
     </row>
     <row r="319" spans="1:16">
       <c r="A319" s="2">
-        <v>1677</v>
+        <v>1377</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>2045</v>
@@ -44692,7 +44692,7 @@
     </row>
     <row r="320" spans="1:16">
       <c r="A320" s="2">
-        <v>1678</v>
+        <v>1378</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>2048</v>
@@ -44742,7 +44742,7 @@
     </row>
     <row r="321" spans="1:16">
       <c r="A321" s="2">
-        <v>1679</v>
+        <v>1379</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>2051</v>
@@ -44792,7 +44792,7 @@
     </row>
     <row r="322" spans="1:16">
       <c r="A322" s="2">
-        <v>1680</v>
+        <v>1380</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>2054</v>
@@ -44842,7 +44842,7 @@
     </row>
     <row r="323" spans="1:16">
       <c r="A323" s="2">
-        <v>1681</v>
+        <v>1381</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>2057</v>
@@ -44892,7 +44892,7 @@
     </row>
     <row r="324" spans="1:16">
       <c r="A324" s="2">
-        <v>1682</v>
+        <v>1382</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>2060</v>
@@ -44942,7 +44942,7 @@
     </row>
     <row r="325" spans="1:16">
       <c r="A325" s="2">
-        <v>1683</v>
+        <v>1383</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>2063</v>
@@ -44992,7 +44992,7 @@
     </row>
     <row r="326" spans="1:16">
       <c r="A326" s="2">
-        <v>1684</v>
+        <v>1384</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>2066</v>
@@ -45042,7 +45042,7 @@
     </row>
     <row r="327" spans="1:16">
       <c r="A327" s="2">
-        <v>1685</v>
+        <v>1385</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>2069</v>
@@ -45092,7 +45092,7 @@
     </row>
     <row r="328" spans="1:16">
       <c r="A328" s="2">
-        <v>1686</v>
+        <v>1386</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>2072</v>
@@ -45142,7 +45142,7 @@
     </row>
     <row r="329" spans="1:16">
       <c r="A329" s="2">
-        <v>1687</v>
+        <v>1387</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>2075</v>
@@ -45192,7 +45192,7 @@
     </row>
     <row r="330" spans="1:16">
       <c r="A330" s="2">
-        <v>1688</v>
+        <v>1388</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>2078</v>
@@ -45242,7 +45242,7 @@
     </row>
     <row r="331" spans="1:16">
       <c r="A331" s="2">
-        <v>1689</v>
+        <v>1389</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>2081</v>
@@ -45292,7 +45292,7 @@
     </row>
     <row r="332" spans="1:16">
       <c r="A332" s="2">
-        <v>1690</v>
+        <v>1390</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>2084</v>
@@ -45342,7 +45342,7 @@
     </row>
     <row r="333" spans="1:16">
       <c r="A333" s="2">
-        <v>1691</v>
+        <v>1391</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>2087</v>
@@ -45392,7 +45392,7 @@
     </row>
     <row r="334" spans="1:16">
       <c r="A334" s="2">
-        <v>1692</v>
+        <v>1392</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>2090</v>
@@ -45442,7 +45442,7 @@
     </row>
     <row r="335" spans="1:16">
       <c r="A335" s="2">
-        <v>1693</v>
+        <v>1393</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>2093</v>
@@ -45492,7 +45492,7 @@
     </row>
     <row r="336" spans="1:16">
       <c r="A336" s="2">
-        <v>1694</v>
+        <v>1394</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>2096</v>
@@ -45542,7 +45542,7 @@
     </row>
     <row r="337" spans="1:16">
       <c r="A337" s="2">
-        <v>1695</v>
+        <v>1395</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>2099</v>
@@ -45592,7 +45592,7 @@
     </row>
     <row r="338" spans="1:16">
       <c r="A338" s="2">
-        <v>1696</v>
+        <v>1396</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>2102</v>
@@ -45642,7 +45642,7 @@
     </row>
     <row r="339" spans="1:16">
       <c r="A339" s="2">
-        <v>1697</v>
+        <v>1397</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>2105</v>
@@ -45692,7 +45692,7 @@
     </row>
     <row r="340" spans="1:16">
       <c r="A340" s="2">
-        <v>1698</v>
+        <v>1398</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>2108</v>
@@ -45742,7 +45742,7 @@
     </row>
     <row r="341" spans="1:16">
       <c r="A341" s="2">
-        <v>1699</v>
+        <v>1399</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>2111</v>
@@ -45792,7 +45792,7 @@
     </row>
     <row r="342" spans="1:16">
       <c r="A342" s="2">
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>2114</v>
@@ -45842,7 +45842,7 @@
     </row>
     <row r="343" spans="1:16">
       <c r="A343" s="2">
-        <v>1701</v>
+        <v>1401</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>2117</v>
@@ -45892,7 +45892,7 @@
     </row>
     <row r="344" spans="1:16">
       <c r="A344" s="2">
-        <v>1702</v>
+        <v>1402</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>2120</v>
@@ -45942,7 +45942,7 @@
     </row>
     <row r="345" spans="1:16">
       <c r="A345" s="2">
-        <v>1703</v>
+        <v>1403</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>2123</v>
@@ -45992,7 +45992,7 @@
     </row>
     <row r="346" spans="1:16">
       <c r="A346" s="2">
-        <v>1704</v>
+        <v>1404</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>2126</v>
@@ -46042,7 +46042,7 @@
     </row>
     <row r="347" spans="1:16">
       <c r="A347" s="2">
-        <v>1705</v>
+        <v>1405</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>2129</v>
@@ -46092,7 +46092,7 @@
     </row>
     <row r="348" spans="1:16">
       <c r="A348" s="2">
-        <v>1706</v>
+        <v>1406</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>2132</v>
@@ -46142,7 +46142,7 @@
     </row>
     <row r="349" spans="1:16">
       <c r="A349" s="2">
-        <v>1707</v>
+        <v>1407</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>2135</v>
@@ -46192,7 +46192,7 @@
     </row>
     <row r="350" spans="1:16">
       <c r="A350" s="2">
-        <v>1708</v>
+        <v>1408</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>2138</v>
@@ -46242,7 +46242,7 @@
     </row>
     <row r="351" spans="1:16">
       <c r="A351" s="2">
-        <v>1709</v>
+        <v>1409</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>2141</v>
@@ -46292,7 +46292,7 @@
     </row>
     <row r="352" spans="1:16">
       <c r="A352" s="2">
-        <v>1710</v>
+        <v>1410</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>2144</v>
@@ -46342,7 +46342,7 @@
     </row>
     <row r="353" spans="1:16">
       <c r="A353" s="2">
-        <v>1711</v>
+        <v>1411</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>2147</v>
@@ -46392,7 +46392,7 @@
     </row>
     <row r="354" spans="1:16">
       <c r="A354" s="2">
-        <v>1712</v>
+        <v>1412</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>2150</v>
@@ -46442,7 +46442,7 @@
     </row>
     <row r="355" spans="1:16">
       <c r="A355" s="2">
-        <v>1713</v>
+        <v>1413</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>2153</v>
@@ -46492,7 +46492,7 @@
     </row>
     <row r="356" spans="1:16">
       <c r="A356" s="2">
-        <v>1714</v>
+        <v>1414</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>2156</v>
@@ -46542,7 +46542,7 @@
     </row>
     <row r="357" spans="1:16">
       <c r="A357" s="2">
-        <v>1715</v>
+        <v>1415</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>2159</v>
@@ -46592,7 +46592,7 @@
     </row>
     <row r="358" spans="1:16">
       <c r="A358" s="2">
-        <v>1716</v>
+        <v>1416</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>2162</v>
@@ -46642,7 +46642,7 @@
     </row>
     <row r="359" spans="1:16">
       <c r="A359" s="2">
-        <v>1717</v>
+        <v>1417</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>2165</v>
@@ -46692,7 +46692,7 @@
     </row>
     <row r="360" spans="1:16">
       <c r="A360" s="2">
-        <v>1718</v>
+        <v>1418</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>2168</v>
@@ -46742,7 +46742,7 @@
     </row>
     <row r="361" spans="1:16">
       <c r="A361" s="2">
-        <v>1719</v>
+        <v>1419</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>2171</v>
@@ -46792,7 +46792,7 @@
     </row>
     <row r="362" spans="1:16">
       <c r="A362" s="2">
-        <v>1720</v>
+        <v>1420</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>2174</v>
@@ -46842,7 +46842,7 @@
     </row>
     <row r="363" spans="1:16">
       <c r="A363" s="2">
-        <v>1721</v>
+        <v>1421</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>2177</v>
@@ -46892,7 +46892,7 @@
     </row>
     <row r="364" spans="1:16">
       <c r="A364" s="2">
-        <v>1722</v>
+        <v>1422</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>2180</v>
@@ -46942,7 +46942,7 @@
     </row>
     <row r="365" spans="1:16">
       <c r="A365" s="2">
-        <v>1723</v>
+        <v>1423</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>2183</v>
@@ -46992,7 +46992,7 @@
     </row>
     <row r="366" spans="1:16">
       <c r="A366" s="2">
-        <v>1724</v>
+        <v>1424</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>2186</v>
@@ -47042,7 +47042,7 @@
     </row>
     <row r="367" spans="1:16">
       <c r="A367" s="2">
-        <v>1725</v>
+        <v>1425</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>2189</v>
@@ -47092,7 +47092,7 @@
     </row>
     <row r="368" spans="1:16">
       <c r="A368" s="2">
-        <v>1726</v>
+        <v>1426</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>2192</v>
@@ -47142,7 +47142,7 @@
     </row>
     <row r="369" spans="1:16">
       <c r="A369" s="2">
-        <v>1727</v>
+        <v>1427</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>2195</v>
@@ -47192,7 +47192,7 @@
     </row>
     <row r="370" spans="1:16">
       <c r="A370" s="2">
-        <v>1728</v>
+        <v>1428</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>2198</v>
@@ -47242,7 +47242,7 @@
     </row>
     <row r="371" spans="1:16">
       <c r="A371" s="2">
-        <v>1729</v>
+        <v>1429</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>2201</v>
@@ -47292,7 +47292,7 @@
     </row>
     <row r="372" spans="1:16">
       <c r="A372" s="2">
-        <v>1730</v>
+        <v>1430</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>2204</v>
@@ -47342,7 +47342,7 @@
     </row>
     <row r="373" spans="1:16">
       <c r="A373" s="2">
-        <v>1731</v>
+        <v>1431</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>2207</v>
@@ -47392,7 +47392,7 @@
     </row>
     <row r="374" spans="1:16">
       <c r="A374" s="2">
-        <v>1732</v>
+        <v>1432</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>2210</v>
@@ -47442,7 +47442,7 @@
     </row>
     <row r="375" spans="1:16">
       <c r="A375" s="2">
-        <v>1733</v>
+        <v>1433</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>2213</v>
@@ -47492,7 +47492,7 @@
     </row>
     <row r="376" spans="1:16">
       <c r="A376" s="2">
-        <v>1734</v>
+        <v>1434</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>2216</v>
@@ -47542,7 +47542,7 @@
     </row>
     <row r="377" spans="1:16">
       <c r="A377" s="2">
-        <v>1735</v>
+        <v>1435</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>2219</v>
@@ -47592,7 +47592,7 @@
     </row>
     <row r="378" spans="1:16">
       <c r="A378" s="2">
-        <v>1736</v>
+        <v>1436</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>2222</v>
@@ -47642,7 +47642,7 @@
     </row>
     <row r="379" spans="1:16">
       <c r="A379" s="2">
-        <v>1737</v>
+        <v>1437</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>2225</v>
@@ -47692,7 +47692,7 @@
     </row>
     <row r="380" spans="1:16">
       <c r="A380" s="2">
-        <v>1738</v>
+        <v>1438</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>2228</v>
@@ -47742,7 +47742,7 @@
     </row>
     <row r="381" spans="1:16">
       <c r="A381" s="2">
-        <v>1739</v>
+        <v>1439</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>2231</v>
@@ -47792,7 +47792,7 @@
     </row>
     <row r="382" spans="1:16">
       <c r="A382" s="2">
-        <v>1740</v>
+        <v>1440</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>2234</v>
@@ -47842,7 +47842,7 @@
     </row>
     <row r="383" spans="1:16">
       <c r="A383" s="2">
-        <v>1741</v>
+        <v>1441</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>2237</v>
@@ -47892,7 +47892,7 @@
     </row>
     <row r="384" spans="1:16">
       <c r="A384" s="2">
-        <v>1742</v>
+        <v>1442</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>2240</v>
@@ -47942,7 +47942,7 @@
     </row>
     <row r="385" spans="1:16">
       <c r="A385" s="2">
-        <v>1743</v>
+        <v>1443</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>2243</v>
@@ -47992,7 +47992,7 @@
     </row>
     <row r="386" spans="1:16">
       <c r="A386" s="2">
-        <v>1744</v>
+        <v>1444</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>2246</v>
@@ -48042,7 +48042,7 @@
     </row>
     <row r="387" spans="1:16">
       <c r="A387" s="2">
-        <v>1745</v>
+        <v>1445</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>2249</v>
@@ -48092,7 +48092,7 @@
     </row>
     <row r="388" spans="1:16">
       <c r="A388" s="2">
-        <v>1746</v>
+        <v>1446</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>2252</v>
@@ -48142,7 +48142,7 @@
     </row>
     <row r="389" spans="1:16">
       <c r="A389" s="2">
-        <v>1747</v>
+        <v>1447</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>2255</v>
@@ -48192,7 +48192,7 @@
     </row>
     <row r="390" spans="1:16">
       <c r="A390" s="2">
-        <v>1748</v>
+        <v>1448</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>2258</v>
@@ -48242,7 +48242,7 @@
     </row>
     <row r="391" spans="1:16">
       <c r="A391" s="2">
-        <v>1749</v>
+        <v>1449</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>2261</v>
@@ -48292,7 +48292,7 @@
     </row>
     <row r="392" spans="1:16">
       <c r="A392" s="2">
-        <v>1750</v>
+        <v>1450</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>2264</v>
@@ -48342,7 +48342,7 @@
     </row>
     <row r="393" spans="1:16">
       <c r="A393" s="2">
-        <v>1751</v>
+        <v>1451</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>2267</v>
@@ -48392,7 +48392,7 @@
     </row>
     <row r="394" spans="1:16">
       <c r="A394" s="2">
-        <v>1752</v>
+        <v>1452</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>2270</v>
@@ -48442,7 +48442,7 @@
     </row>
     <row r="395" spans="1:16">
       <c r="A395" s="2">
-        <v>1753</v>
+        <v>1453</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>2273</v>
@@ -48492,7 +48492,7 @@
     </row>
     <row r="396" spans="1:16">
       <c r="A396" s="2">
-        <v>1754</v>
+        <v>1454</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>2276</v>
@@ -48542,7 +48542,7 @@
     </row>
     <row r="397" spans="1:16">
       <c r="A397" s="2">
-        <v>1755</v>
+        <v>1455</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>2279</v>
@@ -48592,7 +48592,7 @@
     </row>
     <row r="398" spans="1:16">
       <c r="A398" s="2">
-        <v>1756</v>
+        <v>1456</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>2282</v>
@@ -48642,7 +48642,7 @@
     </row>
     <row r="399" spans="1:16">
       <c r="A399" s="2">
-        <v>1757</v>
+        <v>1457</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>2285</v>
@@ -48692,7 +48692,7 @@
     </row>
     <row r="400" spans="1:16">
       <c r="A400" s="2">
-        <v>1758</v>
+        <v>1458</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>2288</v>
@@ -48742,7 +48742,7 @@
     </row>
     <row r="401" spans="1:16">
       <c r="A401" s="2">
-        <v>1759</v>
+        <v>1459</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>2291</v>
@@ -48792,7 +48792,7 @@
     </row>
     <row r="402" spans="1:16">
       <c r="A402" s="2">
-        <v>1760</v>
+        <v>1460</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>2294</v>
@@ -48842,7 +48842,7 @@
     </row>
     <row r="403" spans="1:16">
       <c r="A403" s="2">
-        <v>1761</v>
+        <v>1461</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>2297</v>
@@ -48892,7 +48892,7 @@
     </row>
     <row r="404" spans="1:16">
       <c r="A404" s="2">
-        <v>1762</v>
+        <v>1462</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>2300</v>
@@ -48942,7 +48942,7 @@
     </row>
     <row r="405" spans="1:16">
       <c r="A405" s="2">
-        <v>1763</v>
+        <v>1463</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>2303</v>
@@ -48992,7 +48992,7 @@
     </row>
     <row r="406" spans="1:16">
       <c r="A406" s="2">
-        <v>1764</v>
+        <v>1464</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>2306</v>
@@ -49042,7 +49042,7 @@
     </row>
     <row r="407" spans="1:16">
       <c r="A407" s="2">
-        <v>1765</v>
+        <v>1465</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>2309</v>
@@ -49092,7 +49092,7 @@
     </row>
     <row r="408" spans="1:16">
       <c r="A408" s="2">
-        <v>1766</v>
+        <v>1466</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>2312</v>
@@ -49142,7 +49142,7 @@
     </row>
     <row r="409" spans="1:16">
       <c r="A409" s="2">
-        <v>1767</v>
+        <v>1467</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>2315</v>
@@ -49192,7 +49192,7 @@
     </row>
     <row r="410" spans="1:16">
       <c r="A410" s="2">
-        <v>1768</v>
+        <v>1468</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>2318</v>
@@ -49242,7 +49242,7 @@
     </row>
     <row r="411" spans="1:16">
       <c r="A411" s="2">
-        <v>1769</v>
+        <v>1469</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>2321</v>
@@ -49292,7 +49292,7 @@
     </row>
     <row r="412" spans="1:16">
       <c r="A412" s="2">
-        <v>1770</v>
+        <v>1470</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>2324</v>
@@ -49342,7 +49342,7 @@
     </row>
     <row r="413" spans="1:16">
       <c r="A413" s="2">
-        <v>1771</v>
+        <v>1471</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>2327</v>
@@ -49392,7 +49392,7 @@
     </row>
     <row r="414" spans="1:16">
       <c r="A414" s="2">
-        <v>1772</v>
+        <v>1472</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>2330</v>
@@ -49442,7 +49442,7 @@
     </row>
     <row r="415" spans="1:16">
       <c r="A415" s="2">
-        <v>1773</v>
+        <v>1473</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>2333</v>
@@ -49492,7 +49492,7 @@
     </row>
     <row r="416" spans="1:16">
       <c r="A416" s="2">
-        <v>1774</v>
+        <v>1474</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>2336</v>
@@ -49542,7 +49542,7 @@
     </row>
     <row r="417" spans="1:16">
       <c r="A417" s="2">
-        <v>1775</v>
+        <v>1475</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>2339</v>
@@ -49592,7 +49592,7 @@
     </row>
     <row r="418" spans="1:16">
       <c r="A418" s="2">
-        <v>1776</v>
+        <v>1476</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>2342</v>
@@ -49642,7 +49642,7 @@
     </row>
     <row r="419" spans="1:16">
       <c r="A419" s="2">
-        <v>1777</v>
+        <v>1477</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>2345</v>
@@ -49692,7 +49692,7 @@
     </row>
     <row r="420" spans="1:16">
       <c r="A420" s="2">
-        <v>1778</v>
+        <v>1478</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>2348</v>
@@ -49742,7 +49742,7 @@
     </row>
     <row r="421" spans="1:16">
       <c r="A421" s="2">
-        <v>1779</v>
+        <v>1479</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>2351</v>
@@ -49792,7 +49792,7 @@
     </row>
     <row r="422" spans="1:16">
       <c r="A422" s="2">
-        <v>1780</v>
+        <v>1480</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>2354</v>
@@ -49842,7 +49842,7 @@
     </row>
     <row r="423" spans="1:16">
       <c r="A423" s="2">
-        <v>1781</v>
+        <v>1481</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>2357</v>
@@ -49892,7 +49892,7 @@
     </row>
     <row r="424" spans="1:16">
       <c r="A424" s="2">
-        <v>1782</v>
+        <v>1482</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>2360</v>
@@ -49942,7 +49942,7 @@
     </row>
     <row r="425" spans="1:16">
       <c r="A425" s="2">
-        <v>1783</v>
+        <v>1483</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>2363</v>
@@ -49992,7 +49992,7 @@
     </row>
     <row r="426" spans="1:16">
       <c r="A426" s="2">
-        <v>1784</v>
+        <v>1484</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>2366</v>
@@ -50042,7 +50042,7 @@
     </row>
     <row r="427" spans="1:16">
       <c r="A427" s="2">
-        <v>1785</v>
+        <v>1485</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>2369</v>
@@ -50092,7 +50092,7 @@
     </row>
     <row r="428" spans="1:16">
       <c r="A428" s="2">
-        <v>1786</v>
+        <v>1486</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>2372</v>
@@ -50142,7 +50142,7 @@
     </row>
     <row r="429" spans="1:16">
       <c r="A429" s="2">
-        <v>1787</v>
+        <v>1487</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>2375</v>
@@ -50192,7 +50192,7 @@
     </row>
     <row r="430" spans="1:16">
       <c r="A430" s="2">
-        <v>1788</v>
+        <v>1488</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>2378</v>
@@ -50242,7 +50242,7 @@
     </row>
     <row r="431" spans="1:16">
       <c r="A431" s="2">
-        <v>1789</v>
+        <v>1489</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>2381</v>
@@ -50292,7 +50292,7 @@
     </row>
     <row r="432" spans="1:16">
       <c r="A432" s="2">
-        <v>1790</v>
+        <v>1490</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>2384</v>
@@ -50342,7 +50342,7 @@
     </row>
     <row r="433" spans="1:16">
       <c r="A433" s="2">
-        <v>1791</v>
+        <v>1491</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>2387</v>
@@ -50392,7 +50392,7 @@
     </row>
     <row r="434" spans="1:16">
       <c r="A434" s="2">
-        <v>1792</v>
+        <v>1492</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>2390</v>
@@ -50442,7 +50442,7 @@
     </row>
     <row r="435" spans="1:16">
       <c r="A435" s="2">
-        <v>1793</v>
+        <v>1493</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>2393</v>
@@ -50492,7 +50492,7 @@
     </row>
     <row r="436" spans="1:16">
       <c r="A436" s="2">
-        <v>1794</v>
+        <v>1494</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>2396</v>
@@ -50542,7 +50542,7 @@
     </row>
     <row r="437" spans="1:16">
       <c r="A437" s="2">
-        <v>1795</v>
+        <v>1495</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>2399</v>
@@ -50592,7 +50592,7 @@
     </row>
     <row r="438" spans="1:16">
       <c r="A438" s="2">
-        <v>1796</v>
+        <v>1496</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>2402</v>
@@ -50642,7 +50642,7 @@
     </row>
     <row r="439" spans="1:16">
       <c r="A439" s="2">
-        <v>1797</v>
+        <v>1497</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>2405</v>
@@ -50692,7 +50692,7 @@
     </row>
     <row r="440" spans="1:16">
       <c r="A440" s="2">
-        <v>1798</v>
+        <v>1498</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>2408</v>
@@ -50742,7 +50742,7 @@
     </row>
     <row r="441" spans="1:16">
       <c r="A441" s="2">
-        <v>1799</v>
+        <v>1499</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>2411</v>
@@ -50792,7 +50792,7 @@
     </row>
     <row r="442" spans="1:16">
       <c r="A442" s="2">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>2414</v>
@@ -50842,7 +50842,7 @@
     </row>
     <row r="443" spans="1:16">
       <c r="A443" s="2">
-        <v>1801</v>
+        <v>1501</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>2417</v>
@@ -50892,7 +50892,7 @@
     </row>
     <row r="444" spans="1:16">
       <c r="A444" s="2">
-        <v>1802</v>
+        <v>1502</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>2420</v>
@@ -50942,7 +50942,7 @@
     </row>
     <row r="445" spans="1:16">
       <c r="A445" s="2">
-        <v>1803</v>
+        <v>1503</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>2423</v>
@@ -50992,7 +50992,7 @@
     </row>
     <row r="446" spans="1:16">
       <c r="A446" s="2">
-        <v>1804</v>
+        <v>1504</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>2426</v>
@@ -51042,7 +51042,7 @@
     </row>
     <row r="447" spans="1:16">
       <c r="A447" s="2">
-        <v>1805</v>
+        <v>1505</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>2429</v>
@@ -51092,7 +51092,7 @@
     </row>
     <row r="448" spans="1:16">
       <c r="A448" s="2">
-        <v>1806</v>
+        <v>1506</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>2432</v>
@@ -51142,7 +51142,7 @@
     </row>
     <row r="449" spans="1:16">
       <c r="A449" s="2">
-        <v>1807</v>
+        <v>1507</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>2435</v>
@@ -51192,7 +51192,7 @@
     </row>
     <row r="450" spans="1:16">
       <c r="A450" s="2">
-        <v>1808</v>
+        <v>1508</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>2438</v>
@@ -51242,7 +51242,7 @@
     </row>
     <row r="451" spans="1:16">
       <c r="A451" s="2">
-        <v>1809</v>
+        <v>1509</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>2441</v>
@@ -51292,7 +51292,7 @@
     </row>
     <row r="452" spans="1:16">
       <c r="A452" s="2">
-        <v>1810</v>
+        <v>1510</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>2444</v>
@@ -51342,7 +51342,7 @@
     </row>
     <row r="453" spans="1:16">
       <c r="A453" s="2">
-        <v>1811</v>
+        <v>1511</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>2447</v>
@@ -51392,7 +51392,7 @@
     </row>
     <row r="454" spans="1:16">
       <c r="A454" s="2">
-        <v>1812</v>
+        <v>1512</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>2450</v>
@@ -51442,7 +51442,7 @@
     </row>
     <row r="455" spans="1:16">
       <c r="A455" s="2">
-        <v>1813</v>
+        <v>1513</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>2453</v>
@@ -51492,7 +51492,7 @@
     </row>
     <row r="456" spans="1:16">
       <c r="A456" s="2">
-        <v>1814</v>
+        <v>1514</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>2456</v>
@@ -51542,7 +51542,7 @@
     </row>
     <row r="457" spans="1:16">
       <c r="A457" s="2">
-        <v>1815</v>
+        <v>1515</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>2459</v>
@@ -51592,7 +51592,7 @@
     </row>
     <row r="458" spans="1:16">
       <c r="A458" s="2">
-        <v>1816</v>
+        <v>1516</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>2462</v>
@@ -51642,7 +51642,7 @@
     </row>
     <row r="459" spans="1:16">
       <c r="A459" s="2">
-        <v>1817</v>
+        <v>1517</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>2465</v>
@@ -51692,7 +51692,7 @@
     </row>
     <row r="460" spans="1:16">
       <c r="A460" s="2">
-        <v>1818</v>
+        <v>1518</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>2468</v>
@@ -51742,7 +51742,7 @@
     </row>
     <row r="461" spans="1:16">
       <c r="A461" s="2">
-        <v>1819</v>
+        <v>1519</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>2471</v>
@@ -51792,7 +51792,7 @@
     </row>
     <row r="462" spans="1:16">
       <c r="A462" s="2">
-        <v>1820</v>
+        <v>1520</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>2474</v>
@@ -51842,7 +51842,7 @@
     </row>
     <row r="463" spans="1:16">
       <c r="A463" s="2">
-        <v>1821</v>
+        <v>1521</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>2477</v>
@@ -51892,7 +51892,7 @@
     </row>
     <row r="464" spans="1:16">
       <c r="A464" s="2">
-        <v>1822</v>
+        <v>1522</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>2480</v>
@@ -51942,7 +51942,7 @@
     </row>
     <row r="465" spans="1:16">
       <c r="A465" s="2">
-        <v>1823</v>
+        <v>1523</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>2483</v>
@@ -51992,7 +51992,7 @@
     </row>
     <row r="466" spans="1:16">
       <c r="A466" s="2">
-        <v>1824</v>
+        <v>1524</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>2486</v>
@@ -52042,7 +52042,7 @@
     </row>
     <row r="467" spans="1:16">
       <c r="A467" s="2">
-        <v>1825</v>
+        <v>1525</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>2489</v>
@@ -52092,7 +52092,7 @@
     </row>
     <row r="468" spans="1:16">
       <c r="A468" s="2">
-        <v>1826</v>
+        <v>1526</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>2492</v>
@@ -52142,7 +52142,7 @@
     </row>
     <row r="469" spans="1:16">
       <c r="A469" s="2">
-        <v>1827</v>
+        <v>1527</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>2495</v>
@@ -52192,7 +52192,7 @@
     </row>
     <row r="470" spans="1:16">
       <c r="A470" s="2">
-        <v>1828</v>
+        <v>1528</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>2498</v>
@@ -52242,7 +52242,7 @@
     </row>
     <row r="471" spans="1:16">
       <c r="A471" s="2">
-        <v>1829</v>
+        <v>1529</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>2501</v>
@@ -52292,7 +52292,7 @@
     </row>
     <row r="472" spans="1:16">
       <c r="A472" s="2">
-        <v>1830</v>
+        <v>1530</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>2504</v>
@@ -52342,7 +52342,7 @@
     </row>
     <row r="473" spans="1:16">
       <c r="A473" s="2">
-        <v>1831</v>
+        <v>1531</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>2507</v>
@@ -52392,7 +52392,7 @@
     </row>
     <row r="474" spans="1:16">
       <c r="A474" s="2">
-        <v>1832</v>
+        <v>1532</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>2510</v>
@@ -52442,7 +52442,7 @@
     </row>
     <row r="475" spans="1:16">
       <c r="A475" s="2">
-        <v>1833</v>
+        <v>1533</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>2513</v>
@@ -52492,7 +52492,7 @@
     </row>
     <row r="476" spans="1:16">
       <c r="A476" s="2">
-        <v>1834</v>
+        <v>1534</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>2516</v>
@@ -52542,7 +52542,7 @@
     </row>
     <row r="477" spans="1:16">
       <c r="A477" s="2">
-        <v>1835</v>
+        <v>1535</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>2519</v>
@@ -52592,7 +52592,7 @@
     </row>
     <row r="478" spans="1:16">
       <c r="A478" s="2">
-        <v>1836</v>
+        <v>1536</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>2522</v>
@@ -52642,7 +52642,7 @@
     </row>
     <row r="479" spans="1:16">
       <c r="A479" s="2">
-        <v>1837</v>
+        <v>1537</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>2525</v>
@@ -52692,7 +52692,7 @@
     </row>
     <row r="480" spans="1:16">
       <c r="A480" s="2">
-        <v>1838</v>
+        <v>1538</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>2528</v>
@@ -52742,7 +52742,7 @@
     </row>
     <row r="481" spans="1:16">
       <c r="A481" s="2">
-        <v>1839</v>
+        <v>1539</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>2531</v>
@@ -52792,7 +52792,7 @@
     </row>
     <row r="482" spans="1:16">
       <c r="A482" s="2">
-        <v>1840</v>
+        <v>1540</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>2534</v>
@@ -52842,7 +52842,7 @@
     </row>
     <row r="483" spans="1:16">
       <c r="A483" s="2">
-        <v>1841</v>
+        <v>1541</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>2537</v>
@@ -52892,7 +52892,7 @@
     </row>
     <row r="484" spans="1:16">
       <c r="A484" s="2">
-        <v>1842</v>
+        <v>1542</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>2540</v>
@@ -52942,7 +52942,7 @@
     </row>
     <row r="485" spans="1:16">
       <c r="A485" s="2">
-        <v>1843</v>
+        <v>1543</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>2543</v>
@@ -52992,7 +52992,7 @@
     </row>
     <row r="486" spans="1:16">
       <c r="A486" s="2">
-        <v>1844</v>
+        <v>1544</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>2546</v>
@@ -53042,7 +53042,7 @@
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="2">
-        <v>1845</v>
+        <v>1545</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>2549</v>
@@ -53092,7 +53092,7 @@
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="2">
-        <v>1846</v>
+        <v>1546</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>2552</v>
@@ -53142,7 +53142,7 @@
     </row>
     <row r="489" spans="1:16">
       <c r="A489" s="2">
-        <v>1847</v>
+        <v>1547</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>2555</v>
@@ -53192,7 +53192,7 @@
     </row>
     <row r="490" spans="1:16">
       <c r="A490" s="2">
-        <v>1848</v>
+        <v>1548</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>2558</v>
@@ -53242,7 +53242,7 @@
     </row>
     <row r="491" spans="1:16">
       <c r="A491" s="2">
-        <v>1849</v>
+        <v>1549</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>2561</v>
@@ -53292,7 +53292,7 @@
     </row>
     <row r="492" spans="1:16">
       <c r="A492" s="2">
-        <v>1850</v>
+        <v>1550</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>2564</v>
@@ -53342,7 +53342,7 @@
     </row>
     <row r="493" spans="1:16">
       <c r="A493" s="2">
-        <v>1851</v>
+        <v>1551</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>2567</v>
@@ -53392,7 +53392,7 @@
     </row>
     <row r="494" spans="1:16">
       <c r="A494" s="2">
-        <v>1852</v>
+        <v>1552</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>2570</v>
@@ -53442,7 +53442,7 @@
     </row>
     <row r="495" spans="1:16">
       <c r="A495" s="2">
-        <v>1853</v>
+        <v>1553</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>2573</v>
@@ -53492,7 +53492,7 @@
     </row>
     <row r="496" spans="1:16">
       <c r="A496" s="2">
-        <v>1854</v>
+        <v>1554</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>2576</v>
@@ -53542,7 +53542,7 @@
     </row>
     <row r="497" spans="1:16">
       <c r="A497" s="2">
-        <v>1855</v>
+        <v>1555</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>2579</v>
@@ -53592,7 +53592,7 @@
     </row>
     <row r="498" spans="1:16">
       <c r="A498" s="2">
-        <v>1856</v>
+        <v>1556</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>2582</v>
@@ -53642,7 +53642,7 @@
     </row>
     <row r="499" spans="1:16">
       <c r="A499" s="2">
-        <v>1857</v>
+        <v>1557</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>2585</v>
@@ -53692,7 +53692,7 @@
     </row>
     <row r="500" spans="1:16">
       <c r="A500" s="2">
-        <v>1858</v>
+        <v>1558</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>2588</v>
@@ -53742,7 +53742,7 @@
     </row>
     <row r="501" spans="1:16">
       <c r="A501" s="2">
-        <v>1859</v>
+        <v>1559</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>2591</v>
@@ -53792,7 +53792,7 @@
     </row>
     <row r="502" spans="1:16">
       <c r="A502" s="2">
-        <v>1860</v>
+        <v>1560</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>2594</v>
@@ -53842,7 +53842,7 @@
     </row>
     <row r="503" spans="1:16">
       <c r="A503" s="2">
-        <v>1861</v>
+        <v>1561</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>2597</v>
@@ -53892,7 +53892,7 @@
     </row>
     <row r="504" spans="1:16">
       <c r="A504" s="2">
-        <v>1862</v>
+        <v>1562</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>2600</v>
@@ -53942,7 +53942,7 @@
     </row>
     <row r="505" spans="1:16">
       <c r="A505" s="2">
-        <v>1863</v>
+        <v>1563</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>2603</v>
@@ -53992,7 +53992,7 @@
     </row>
     <row r="506" spans="1:16">
       <c r="A506" s="2">
-        <v>1864</v>
+        <v>1564</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>2606</v>
@@ -54042,7 +54042,7 @@
     </row>
     <row r="507" spans="1:16">
       <c r="A507" s="2">
-        <v>1865</v>
+        <v>1565</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>2609</v>
@@ -54092,7 +54092,7 @@
     </row>
     <row r="508" spans="1:16">
       <c r="A508" s="2">
-        <v>1866</v>
+        <v>1566</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>2612</v>
@@ -54142,7 +54142,7 @@
     </row>
     <row r="509" spans="1:16">
       <c r="A509" s="2">
-        <v>1867</v>
+        <v>1567</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>2615</v>
@@ -54192,7 +54192,7 @@
     </row>
     <row r="510" spans="1:16">
       <c r="A510" s="2">
-        <v>1868</v>
+        <v>1568</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>2618</v>
@@ -54242,7 +54242,7 @@
     </row>
     <row r="511" spans="1:16">
       <c r="A511" s="2">
-        <v>1869</v>
+        <v>1569</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>2621</v>
@@ -54292,7 +54292,7 @@
     </row>
     <row r="512" spans="1:16">
       <c r="A512" s="2">
-        <v>1870</v>
+        <v>1570</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>2624</v>
@@ -54342,7 +54342,7 @@
     </row>
     <row r="513" spans="1:16">
       <c r="A513" s="2">
-        <v>1871</v>
+        <v>1571</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>2627</v>
@@ -54392,7 +54392,7 @@
     </row>
     <row r="514" spans="1:16">
       <c r="A514" s="2">
-        <v>1872</v>
+        <v>1572</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>2630</v>
@@ -54442,7 +54442,7 @@
     </row>
     <row r="515" spans="1:16">
       <c r="A515" s="2">
-        <v>1873</v>
+        <v>1573</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>2633</v>
@@ -54492,7 +54492,7 @@
     </row>
     <row r="516" spans="1:16">
       <c r="A516" s="2">
-        <v>1874</v>
+        <v>1574</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>2636</v>
@@ -54542,7 +54542,7 @@
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="2">
-        <v>1875</v>
+        <v>1575</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>2639</v>
@@ -54592,7 +54592,7 @@
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="2">
-        <v>1876</v>
+        <v>1576</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>2642</v>
@@ -54642,7 +54642,7 @@
     </row>
     <row r="519" spans="1:16">
       <c r="A519" s="2">
-        <v>1877</v>
+        <v>1577</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>2645</v>
@@ -54692,7 +54692,7 @@
     </row>
     <row r="520" spans="1:16">
       <c r="A520" s="2">
-        <v>1878</v>
+        <v>1578</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>2648</v>
@@ -54742,7 +54742,7 @@
     </row>
     <row r="521" spans="1:16">
       <c r="A521" s="2">
-        <v>1879</v>
+        <v>1579</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>2651</v>
@@ -54792,7 +54792,7 @@
     </row>
     <row r="522" spans="1:16">
       <c r="A522" s="2">
-        <v>1880</v>
+        <v>1580</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>2654</v>
@@ -54842,7 +54842,7 @@
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="2">
-        <v>1881</v>
+        <v>1581</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>2657</v>
@@ -54892,7 +54892,7 @@
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="2">
-        <v>1882</v>
+        <v>1582</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>2660</v>
@@ -54942,7 +54942,7 @@
     </row>
     <row r="525" spans="1:16">
       <c r="A525" s="2">
-        <v>1883</v>
+        <v>1583</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>2663</v>
@@ -54992,7 +54992,7 @@
     </row>
     <row r="526" spans="1:16">
       <c r="A526" s="2">
-        <v>1884</v>
+        <v>1584</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>2666</v>
@@ -55042,7 +55042,7 @@
     </row>
     <row r="527" spans="1:16">
       <c r="A527" s="2">
-        <v>1885</v>
+        <v>1585</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>2669</v>
@@ -55092,7 +55092,7 @@
     </row>
     <row r="528" spans="1:16">
       <c r="A528" s="2">
-        <v>1886</v>
+        <v>1586</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>2672</v>
@@ -55142,7 +55142,7 @@
     </row>
     <row r="529" spans="1:16">
       <c r="A529" s="2">
-        <v>1887</v>
+        <v>1587</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>2675</v>
@@ -55192,7 +55192,7 @@
     </row>
     <row r="530" spans="1:16">
       <c r="A530" s="2">
-        <v>1888</v>
+        <v>1588</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>2678</v>
@@ -55242,7 +55242,7 @@
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="2">
-        <v>1889</v>
+        <v>1589</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>2681</v>
@@ -55292,7 +55292,7 @@
     </row>
     <row r="532" spans="1:16">
       <c r="A532" s="2">
-        <v>1890</v>
+        <v>1590</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>2684</v>
@@ -55342,7 +55342,7 @@
     </row>
     <row r="533" spans="1:16">
       <c r="A533" s="2">
-        <v>1891</v>
+        <v>1591</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>2687</v>
@@ -55392,7 +55392,7 @@
     </row>
     <row r="534" spans="1:16">
       <c r="A534" s="2">
-        <v>1892</v>
+        <v>1592</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>2690</v>
@@ -55442,7 +55442,7 @@
     </row>
     <row r="535" spans="1:16">
       <c r="A535" s="2">
-        <v>1893</v>
+        <v>1593</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>2693</v>
@@ -55492,7 +55492,7 @@
     </row>
     <row r="536" spans="1:16">
       <c r="A536" s="2">
-        <v>1894</v>
+        <v>1594</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>2696</v>
@@ -55542,7 +55542,7 @@
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="2">
-        <v>1895</v>
+        <v>1595</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>2699</v>
@@ -55592,7 +55592,7 @@
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="2">
-        <v>1896</v>
+        <v>1596</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>2702</v>
@@ -55642,7 +55642,7 @@
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="2">
-        <v>1897</v>
+        <v>1597</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>2705</v>
@@ -55692,7 +55692,7 @@
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="2">
-        <v>1898</v>
+        <v>1598</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>2708</v>
@@ -55742,7 +55742,7 @@
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="2">
-        <v>1899</v>
+        <v>1599</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>2711</v>
@@ -55792,7 +55792,7 @@
     </row>
     <row r="542" spans="1:16">
       <c r="A542" s="2">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>2714</v>
@@ -55842,7 +55842,7 @@
     </row>
     <row r="543" spans="1:16">
       <c r="A543" s="2">
-        <v>1901</v>
+        <v>1601</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>2717</v>
@@ -55892,7 +55892,7 @@
     </row>
     <row r="544" spans="1:16">
       <c r="A544" s="2">
-        <v>1902</v>
+        <v>1602</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>2720</v>
@@ -55942,7 +55942,7 @@
     </row>
     <row r="545" spans="1:16">
       <c r="A545" s="2">
-        <v>1903</v>
+        <v>1603</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>2723</v>
@@ -55992,7 +55992,7 @@
     </row>
     <row r="546" spans="1:16">
       <c r="A546" s="2">
-        <v>1904</v>
+        <v>1604</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>2726</v>
@@ -56042,7 +56042,7 @@
     </row>
     <row r="547" spans="1:16">
       <c r="A547" s="2">
-        <v>1905</v>
+        <v>1605</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>2729</v>
@@ -56092,7 +56092,7 @@
     </row>
     <row r="548" spans="1:16">
       <c r="A548" s="2">
-        <v>1906</v>
+        <v>1606</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>2732</v>
@@ -56142,7 +56142,7 @@
     </row>
     <row r="549" spans="1:16">
       <c r="A549" s="2">
-        <v>1907</v>
+        <v>1607</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>2735</v>
@@ -56192,7 +56192,7 @@
     </row>
     <row r="550" spans="1:16">
       <c r="A550" s="2">
-        <v>1908</v>
+        <v>1608</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>2738</v>
@@ -56242,7 +56242,7 @@
     </row>
     <row r="551" spans="1:16">
       <c r="A551" s="2">
-        <v>1909</v>
+        <v>1609</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>2741</v>
@@ -56292,7 +56292,7 @@
     </row>
     <row r="552" spans="1:16">
       <c r="A552" s="2">
-        <v>1910</v>
+        <v>1610</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>2744</v>
@@ -56342,7 +56342,7 @@
     </row>
     <row r="553" spans="1:16">
       <c r="A553" s="2">
-        <v>1911</v>
+        <v>1611</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>2747</v>
@@ -56392,7 +56392,7 @@
     </row>
     <row r="554" spans="1:16">
       <c r="A554" s="2">
-        <v>1912</v>
+        <v>1612</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>2750</v>
@@ -56442,7 +56442,7 @@
     </row>
     <row r="555" spans="1:16">
       <c r="A555" s="2">
-        <v>1913</v>
+        <v>1613</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>2753</v>
@@ -56492,7 +56492,7 @@
     </row>
     <row r="556" spans="1:16">
       <c r="A556" s="2">
-        <v>1914</v>
+        <v>1614</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>2756</v>
@@ -56542,7 +56542,7 @@
     </row>
     <row r="557" spans="1:16">
       <c r="A557" s="2">
-        <v>1915</v>
+        <v>1615</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>2759</v>
@@ -56592,7 +56592,7 @@
     </row>
     <row r="558" spans="1:16">
       <c r="A558" s="2">
-        <v>1916</v>
+        <v>1616</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>2762</v>
@@ -56642,7 +56642,7 @@
     </row>
     <row r="559" spans="1:16">
       <c r="A559" s="2">
-        <v>1917</v>
+        <v>1617</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>2765</v>
@@ -56692,7 +56692,7 @@
     </row>
     <row r="560" spans="1:16">
       <c r="A560" s="2">
-        <v>1918</v>
+        <v>1618</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>2768</v>
@@ -56742,7 +56742,7 @@
     </row>
     <row r="561" spans="1:16">
       <c r="A561" s="2">
-        <v>1919</v>
+        <v>1619</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>2771</v>
@@ -56792,7 +56792,7 @@
     </row>
     <row r="562" spans="1:16">
       <c r="A562" s="2">
-        <v>1920</v>
+        <v>1620</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>2774</v>
@@ -56842,7 +56842,7 @@
     </row>
     <row r="563" spans="1:16">
       <c r="A563" s="2">
-        <v>1921</v>
+        <v>1621</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>2777</v>
@@ -56892,7 +56892,7 @@
     </row>
     <row r="564" spans="1:16">
       <c r="A564" s="2">
-        <v>1922</v>
+        <v>1622</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>2780</v>
@@ -56942,7 +56942,7 @@
     </row>
     <row r="565" spans="1:16">
       <c r="A565" s="2">
-        <v>1923</v>
+        <v>1623</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>2783</v>
@@ -56992,7 +56992,7 @@
     </row>
     <row r="566" spans="1:16">
       <c r="A566" s="2">
-        <v>1924</v>
+        <v>1624</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>2786</v>
@@ -57042,7 +57042,7 @@
     </row>
     <row r="567" spans="1:16">
       <c r="A567" s="2">
-        <v>1925</v>
+        <v>1625</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>2789</v>
@@ -57092,7 +57092,7 @@
     </row>
     <row r="568" spans="1:16">
       <c r="A568" s="2">
-        <v>1926</v>
+        <v>1626</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>2792</v>
@@ -57142,7 +57142,7 @@
     </row>
     <row r="569" spans="1:16">
       <c r="A569" s="2">
-        <v>1927</v>
+        <v>1627</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>2795</v>
@@ -57192,7 +57192,7 @@
     </row>
     <row r="570" spans="1:16">
       <c r="A570" s="2">
-        <v>1928</v>
+        <v>1628</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>2798</v>
@@ -57242,7 +57242,7 @@
     </row>
     <row r="571" spans="1:16">
       <c r="A571" s="2">
-        <v>1929</v>
+        <v>1629</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>2801</v>
@@ -57292,7 +57292,7 @@
     </row>
     <row r="572" spans="1:16">
       <c r="A572" s="2">
-        <v>1930</v>
+        <v>1630</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>2804</v>
@@ -57342,7 +57342,7 @@
     </row>
     <row r="573" spans="1:16">
       <c r="A573" s="2">
-        <v>1931</v>
+        <v>1631</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>2807</v>
@@ -57392,7 +57392,7 @@
     </row>
     <row r="574" spans="1:16">
       <c r="A574" s="2">
-        <v>1932</v>
+        <v>1632</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>2810</v>
@@ -57442,7 +57442,7 @@
     </row>
     <row r="575" spans="1:16">
       <c r="A575" s="2">
-        <v>1933</v>
+        <v>1633</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>2813</v>
@@ -57492,7 +57492,7 @@
     </row>
     <row r="576" spans="1:16">
       <c r="A576" s="2">
-        <v>1934</v>
+        <v>1634</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>2816</v>
@@ -57542,7 +57542,7 @@
     </row>
     <row r="577" spans="1:16">
       <c r="A577" s="2">
-        <v>1935</v>
+        <v>1635</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>2819</v>
@@ -57592,7 +57592,7 @@
     </row>
     <row r="578" spans="1:16">
       <c r="A578" s="2">
-        <v>1936</v>
+        <v>1636</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>2822</v>
@@ -57642,7 +57642,7 @@
     </row>
     <row r="579" spans="1:16">
       <c r="A579" s="2">
-        <v>1937</v>
+        <v>1637</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>2825</v>
@@ -57692,7 +57692,7 @@
     </row>
     <row r="580" spans="1:16">
       <c r="A580" s="2">
-        <v>1938</v>
+        <v>1638</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>2828</v>
@@ -57742,7 +57742,7 @@
     </row>
     <row r="581" spans="1:16">
       <c r="A581" s="2">
-        <v>1939</v>
+        <v>1639</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>2831</v>
@@ -57792,7 +57792,7 @@
     </row>
     <row r="582" spans="1:16">
       <c r="A582" s="2">
-        <v>1940</v>
+        <v>1640</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>2834</v>
@@ -57842,7 +57842,7 @@
     </row>
     <row r="583" spans="1:16">
       <c r="A583" s="2">
-        <v>1941</v>
+        <v>1641</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>2837</v>
@@ -57892,7 +57892,7 @@
     </row>
     <row r="584" spans="1:16">
       <c r="A584" s="2">
-        <v>1942</v>
+        <v>1642</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>2840</v>
@@ -57942,7 +57942,7 @@
     </row>
     <row r="585" spans="1:16">
       <c r="A585" s="2">
-        <v>1943</v>
+        <v>1643</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>2843</v>
@@ -57992,7 +57992,7 @@
     </row>
     <row r="586" spans="1:16">
       <c r="A586" s="2">
-        <v>1944</v>
+        <v>1644</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>2846</v>
@@ -58042,7 +58042,7 @@
     </row>
     <row r="587" spans="1:16">
       <c r="A587" s="2">
-        <v>1945</v>
+        <v>1645</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>2849</v>
@@ -58092,7 +58092,7 @@
     </row>
     <row r="588" spans="1:16">
       <c r="A588" s="2">
-        <v>1946</v>
+        <v>1646</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>2852</v>
@@ -58142,7 +58142,7 @@
     </row>
     <row r="589" spans="1:16">
       <c r="A589" s="2">
-        <v>1947</v>
+        <v>1647</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>2855</v>
@@ -58192,7 +58192,7 @@
     </row>
     <row r="590" spans="1:16">
       <c r="A590" s="2">
-        <v>1948</v>
+        <v>1648</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>2858</v>
@@ -58242,7 +58242,7 @@
     </row>
     <row r="591" spans="1:16">
       <c r="A591" s="2">
-        <v>1949</v>
+        <v>1649</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>2861</v>
@@ -58292,7 +58292,7 @@
     </row>
     <row r="592" spans="1:16">
       <c r="A592" s="2">
-        <v>1950</v>
+        <v>1650</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>2864</v>
@@ -58342,7 +58342,7 @@
     </row>
     <row r="593" spans="1:16">
       <c r="A593" s="2">
-        <v>1951</v>
+        <v>1651</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>2867</v>
@@ -58392,7 +58392,7 @@
     </row>
     <row r="594" spans="1:16">
       <c r="A594" s="2">
-        <v>1952</v>
+        <v>1652</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>2870</v>
@@ -58442,7 +58442,7 @@
     </row>
     <row r="595" spans="1:16">
       <c r="A595" s="2">
-        <v>1953</v>
+        <v>1653</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>2873</v>
@@ -58492,7 +58492,7 @@
     </row>
     <row r="596" spans="1:16">
       <c r="A596" s="2">
-        <v>1954</v>
+        <v>1654</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>2876</v>
@@ -58542,7 +58542,7 @@
     </row>
     <row r="597" spans="1:16">
       <c r="A597" s="2">
-        <v>1955</v>
+        <v>1655</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>2879</v>
@@ -58592,7 +58592,7 @@
     </row>
     <row r="598" spans="1:16">
       <c r="A598" s="2">
-        <v>1956</v>
+        <v>1656</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>2882</v>
@@ -58642,7 +58642,7 @@
     </row>
     <row r="599" spans="1:16">
       <c r="A599" s="2">
-        <v>1957</v>
+        <v>1657</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>2885</v>
@@ -58692,7 +58692,7 @@
     </row>
     <row r="600" spans="1:16">
       <c r="A600" s="2">
-        <v>1958</v>
+        <v>1658</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>2888</v>
@@ -58742,7 +58742,7 @@
     </row>
     <row r="601" spans="1:16">
       <c r="A601" s="2">
-        <v>1959</v>
+        <v>1659</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>2891</v>
@@ -58792,7 +58792,7 @@
     </row>
     <row r="602" spans="1:16">
       <c r="A602" s="2">
-        <v>1960</v>
+        <v>1660</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>2894</v>
@@ -58842,7 +58842,7 @@
     </row>
     <row r="603" spans="1:16">
       <c r="A603" s="2">
-        <v>1961</v>
+        <v>1661</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>2897</v>
@@ -58892,7 +58892,7 @@
     </row>
     <row r="604" spans="1:16">
       <c r="A604" s="2">
-        <v>1962</v>
+        <v>1662</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>2900</v>
@@ -58942,7 +58942,7 @@
     </row>
     <row r="605" spans="1:16">
       <c r="A605" s="2">
-        <v>1963</v>
+        <v>1663</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>2903</v>
@@ -58992,7 +58992,7 @@
     </row>
     <row r="606" spans="1:16">
       <c r="A606" s="2">
-        <v>1964</v>
+        <v>1664</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>2906</v>
@@ -59042,7 +59042,7 @@
     </row>
     <row r="607" spans="1:16">
       <c r="A607" s="2">
-        <v>1965</v>
+        <v>1665</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>2909</v>
@@ -59092,7 +59092,7 @@
     </row>
     <row r="608" spans="1:16">
       <c r="A608" s="2">
-        <v>1966</v>
+        <v>1666</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>2912</v>
@@ -59142,7 +59142,7 @@
     </row>
     <row r="609" spans="1:16">
       <c r="A609" s="2">
-        <v>1967</v>
+        <v>1667</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>2915</v>
@@ -59192,7 +59192,7 @@
     </row>
     <row r="610" spans="1:16">
       <c r="A610" s="2">
-        <v>1968</v>
+        <v>1668</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>2918</v>
@@ -59242,7 +59242,7 @@
     </row>
     <row r="611" spans="1:16">
       <c r="A611" s="2">
-        <v>1969</v>
+        <v>1669</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>2921</v>
@@ -59292,7 +59292,7 @@
     </row>
     <row r="612" spans="1:16">
       <c r="A612" s="2">
-        <v>1970</v>
+        <v>1670</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>2924</v>
@@ -59342,7 +59342,7 @@
     </row>
     <row r="613" spans="1:16">
       <c r="A613" s="2">
-        <v>1971</v>
+        <v>1671</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>2927</v>
@@ -59392,7 +59392,7 @@
     </row>
     <row r="614" spans="1:16">
       <c r="A614" s="2">
-        <v>1972</v>
+        <v>1672</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>2930</v>
@@ -59442,7 +59442,7 @@
     </row>
     <row r="615" spans="1:16">
       <c r="A615" s="2">
-        <v>1973</v>
+        <v>1673</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>2933</v>
@@ -59492,7 +59492,7 @@
     </row>
     <row r="616" spans="1:16">
       <c r="A616" s="2">
-        <v>1974</v>
+        <v>1674</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>2936</v>
@@ -59542,7 +59542,7 @@
     </row>
     <row r="617" spans="1:16">
       <c r="A617" s="2">
-        <v>1975</v>
+        <v>1675</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>2939</v>
@@ -59592,7 +59592,7 @@
     </row>
     <row r="618" spans="1:16">
       <c r="A618" s="2">
-        <v>1976</v>
+        <v>1676</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>2942</v>
@@ -59642,7 +59642,7 @@
     </row>
     <row r="619" spans="1:16">
       <c r="A619" s="2">
-        <v>1977</v>
+        <v>1677</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>2945</v>
@@ -59692,7 +59692,7 @@
     </row>
     <row r="620" spans="1:16">
       <c r="A620" s="2">
-        <v>1978</v>
+        <v>1678</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>2948</v>
@@ -59742,7 +59742,7 @@
     </row>
     <row r="621" spans="1:16">
       <c r="A621" s="2">
-        <v>1979</v>
+        <v>1679</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>2951</v>
@@ -59792,7 +59792,7 @@
     </row>
     <row r="622" spans="1:16">
       <c r="A622" s="2">
-        <v>1980</v>
+        <v>1680</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>2954</v>
@@ -59842,7 +59842,7 @@
     </row>
     <row r="623" spans="1:16">
       <c r="A623" s="2">
-        <v>1981</v>
+        <v>1681</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>2957</v>
@@ -59892,7 +59892,7 @@
     </row>
     <row r="624" spans="1:16">
       <c r="A624" s="2">
-        <v>1982</v>
+        <v>1682</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>2960</v>
@@ -59942,7 +59942,7 @@
     </row>
     <row r="625" spans="1:16">
       <c r="A625" s="2">
-        <v>1983</v>
+        <v>1683</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>2963</v>
@@ -59992,7 +59992,7 @@
     </row>
     <row r="626" spans="1:16">
       <c r="A626" s="2">
-        <v>1984</v>
+        <v>1684</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>2966</v>
@@ -60042,7 +60042,7 @@
     </row>
     <row r="627" spans="1:16">
       <c r="A627" s="2">
-        <v>1985</v>
+        <v>1685</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>2969</v>
@@ -60092,7 +60092,7 @@
     </row>
     <row r="628" spans="1:16">
       <c r="A628" s="2">
-        <v>1986</v>
+        <v>1686</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>2972</v>
@@ -60142,7 +60142,7 @@
     </row>
     <row r="629" spans="1:16">
       <c r="A629" s="2">
-        <v>1987</v>
+        <v>1687</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>2975</v>
@@ -60192,7 +60192,7 @@
     </row>
     <row r="630" spans="1:16">
       <c r="A630" s="2">
-        <v>1988</v>
+        <v>1688</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>2978</v>
@@ -60242,7 +60242,7 @@
     </row>
     <row r="631" spans="1:16">
       <c r="A631" s="2">
-        <v>1989</v>
+        <v>1689</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>2981</v>
@@ -60292,7 +60292,7 @@
     </row>
     <row r="632" spans="1:16">
       <c r="A632" s="2">
-        <v>1990</v>
+        <v>1690</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>2984</v>
@@ -60342,7 +60342,7 @@
     </row>
     <row r="633" spans="1:16">
       <c r="A633" s="2">
-        <v>1991</v>
+        <v>1691</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>2987</v>
@@ -60392,7 +60392,7 @@
     </row>
     <row r="634" spans="1:16">
       <c r="A634" s="2">
-        <v>1992</v>
+        <v>1692</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>2990</v>
@@ -60442,7 +60442,7 @@
     </row>
     <row r="635" spans="1:16">
       <c r="A635" s="2">
-        <v>1993</v>
+        <v>1693</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>2993</v>
@@ -60492,7 +60492,7 @@
     </row>
     <row r="636" spans="1:16">
       <c r="A636" s="2">
-        <v>1994</v>
+        <v>1694</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>2996</v>
@@ -60542,7 +60542,7 @@
     </row>
     <row r="637" spans="1:16">
       <c r="A637" s="2">
-        <v>1995</v>
+        <v>1695</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>2999</v>
@@ -60592,7 +60592,7 @@
     </row>
     <row r="638" spans="1:16">
       <c r="A638" s="2">
-        <v>1996</v>
+        <v>1696</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>3002</v>
@@ -60642,7 +60642,7 @@
     </row>
     <row r="639" spans="1:16">
       <c r="A639" s="2">
-        <v>1997</v>
+        <v>1697</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>3005</v>
@@ -60692,7 +60692,7 @@
     </row>
     <row r="640" spans="1:16">
       <c r="A640" s="2">
-        <v>1998</v>
+        <v>1698</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>3008</v>
@@ -60742,7 +60742,7 @@
     </row>
     <row r="641" spans="1:16">
       <c r="A641" s="2">
-        <v>1999</v>
+        <v>1699</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>3011</v>
@@ -60792,7 +60792,7 @@
     </row>
     <row r="642" spans="1:16">
       <c r="A642" s="2">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>3014</v>
@@ -60842,7 +60842,7 @@
     </row>
     <row r="643" spans="1:16">
       <c r="A643" s="2">
-        <v>2001</v>
+        <v>1701</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>3017</v>
@@ -60892,7 +60892,7 @@
     </row>
     <row r="644" spans="1:16">
       <c r="A644" s="2">
-        <v>2002</v>
+        <v>1702</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>3020</v>
@@ -60942,7 +60942,7 @@
     </row>
     <row r="645" spans="1:16">
       <c r="A645" s="2">
-        <v>2003</v>
+        <v>1703</v>
       </c>
       <c r="B645" s="2" t="s">
         <v>3023</v>
@@ -60992,7 +60992,7 @@
     </row>
     <row r="646" spans="1:16">
       <c r="A646" s="2">
-        <v>2004</v>
+        <v>1704</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>3026</v>
@@ -61042,7 +61042,7 @@
     </row>
     <row r="647" spans="1:16">
       <c r="A647" s="2">
-        <v>2005</v>
+        <v>1705</v>
       </c>
       <c r="B647" s="2" t="s">
         <v>3029</v>
@@ -61092,7 +61092,7 @@
     </row>
     <row r="648" spans="1:16">
       <c r="A648" s="2">
-        <v>2006</v>
+        <v>1706</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>3032</v>
@@ -61142,7 +61142,7 @@
     </row>
     <row r="649" spans="1:16">
       <c r="A649" s="2">
-        <v>2007</v>
+        <v>1707</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>3035</v>
@@ -61192,7 +61192,7 @@
     </row>
     <row r="650" spans="1:16">
       <c r="A650" s="2">
-        <v>2008</v>
+        <v>1708</v>
       </c>
       <c r="B650" s="2" t="s">
         <v>3038</v>
@@ -61242,7 +61242,7 @@
     </row>
     <row r="651" spans="1:16">
       <c r="A651" s="2">
-        <v>2009</v>
+        <v>1709</v>
       </c>
       <c r="B651" s="2" t="s">
         <v>3041</v>
@@ -61292,7 +61292,7 @@
     </row>
     <row r="652" spans="1:16">
       <c r="A652" s="2">
-        <v>2010</v>
+        <v>1710</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>3044</v>
@@ -61342,7 +61342,7 @@
     </row>
     <row r="653" spans="1:16">
       <c r="A653" s="2">
-        <v>2011</v>
+        <v>1711</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>3047</v>
@@ -61392,7 +61392,7 @@
     </row>
     <row r="654" spans="1:16">
       <c r="A654" s="2">
-        <v>2012</v>
+        <v>1712</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>3050</v>
@@ -61442,7 +61442,7 @@
     </row>
     <row r="655" spans="1:16">
       <c r="A655" s="2">
-        <v>2013</v>
+        <v>1713</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>3053</v>
@@ -61492,7 +61492,7 @@
     </row>
     <row r="656" spans="1:16">
       <c r="A656" s="2">
-        <v>2014</v>
+        <v>1714</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>3056</v>
@@ -61542,7 +61542,7 @@
     </row>
     <row r="657" spans="1:16">
       <c r="A657" s="2">
-        <v>2015</v>
+        <v>1715</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>3059</v>
@@ -61592,7 +61592,7 @@
     </row>
     <row r="658" spans="1:16">
       <c r="A658" s="2">
-        <v>2016</v>
+        <v>1716</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>3062</v>
@@ -61642,7 +61642,7 @@
     </row>
     <row r="659" spans="1:16">
       <c r="A659" s="2">
-        <v>2017</v>
+        <v>1717</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>3065</v>
@@ -61692,7 +61692,7 @@
     </row>
     <row r="660" spans="1:16">
       <c r="A660" s="2">
-        <v>2018</v>
+        <v>1718</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>3068</v>
@@ -61742,7 +61742,7 @@
     </row>
     <row r="661" spans="1:16">
       <c r="A661" s="2">
-        <v>2019</v>
+        <v>1719</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>3071</v>
@@ -61792,7 +61792,7 @@
     </row>
     <row r="662" spans="1:16">
       <c r="A662" s="2">
-        <v>2020</v>
+        <v>1720</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>3074</v>
@@ -61842,7 +61842,7 @@
     </row>
     <row r="663" spans="1:16">
       <c r="A663" s="2">
-        <v>2021</v>
+        <v>1721</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>3077</v>
@@ -61892,7 +61892,7 @@
     </row>
     <row r="664" spans="1:16">
       <c r="A664" s="2">
-        <v>2022</v>
+        <v>1722</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>3080</v>
@@ -61942,7 +61942,7 @@
     </row>
     <row r="665" spans="1:16">
       <c r="A665" s="2">
-        <v>2023</v>
+        <v>1723</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>3083</v>
@@ -61992,7 +61992,7 @@
     </row>
     <row r="666" spans="1:16">
       <c r="A666" s="2">
-        <v>2024</v>
+        <v>1724</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>3086</v>
@@ -62042,7 +62042,7 @@
     </row>
     <row r="667" spans="1:16">
       <c r="A667" s="2">
-        <v>2025</v>
+        <v>1725</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>3089</v>
@@ -62092,7 +62092,7 @@
     </row>
     <row r="668" spans="1:16">
       <c r="A668" s="2">
-        <v>2026</v>
+        <v>1726</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>3092</v>
@@ -62142,7 +62142,7 @@
     </row>
     <row r="669" spans="1:16">
       <c r="A669" s="2">
-        <v>2027</v>
+        <v>1727</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>3095</v>
@@ -62192,7 +62192,7 @@
     </row>
     <row r="670" spans="1:16">
       <c r="A670" s="2">
-        <v>2028</v>
+        <v>1728</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>3098</v>
@@ -62242,7 +62242,7 @@
     </row>
     <row r="671" spans="1:16">
       <c r="A671" s="2">
-        <v>2029</v>
+        <v>1729</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>3101</v>
@@ -62292,7 +62292,7 @@
     </row>
     <row r="672" spans="1:16">
       <c r="A672" s="2">
-        <v>2030</v>
+        <v>1730</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>3104</v>
@@ -62342,7 +62342,7 @@
     </row>
     <row r="673" spans="1:16">
       <c r="A673" s="2">
-        <v>2031</v>
+        <v>1731</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>3107</v>
@@ -62392,7 +62392,7 @@
     </row>
     <row r="674" spans="1:16">
       <c r="A674" s="2">
-        <v>2032</v>
+        <v>1732</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>3110</v>
@@ -62442,7 +62442,7 @@
     </row>
     <row r="675" spans="1:16">
       <c r="A675" s="2">
-        <v>2033</v>
+        <v>1733</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>3113</v>
@@ -62492,7 +62492,7 @@
     </row>
     <row r="676" spans="1:16">
       <c r="A676" s="2">
-        <v>2034</v>
+        <v>1734</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>3116</v>
@@ -62542,7 +62542,7 @@
     </row>
     <row r="677" spans="1:16">
       <c r="A677" s="2">
-        <v>2035</v>
+        <v>1735</v>
       </c>
       <c r="B677" s="2" t="s">
         <v>3119</v>
@@ -62592,7 +62592,7 @@
     </row>
     <row r="678" spans="1:16">
       <c r="A678" s="2">
-        <v>2036</v>
+        <v>1736</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>3122</v>
@@ -62642,7 +62642,7 @@
     </row>
     <row r="679" spans="1:16">
       <c r="A679" s="2">
-        <v>2037</v>
+        <v>1737</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>3125</v>
@@ -62692,7 +62692,7 @@
     </row>
     <row r="680" spans="1:16">
       <c r="A680" s="2">
-        <v>2038</v>
+        <v>1738</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>3128</v>
@@ -62742,7 +62742,7 @@
     </row>
     <row r="681" spans="1:16">
       <c r="A681" s="2">
-        <v>2039</v>
+        <v>1739</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>3131</v>
@@ -62792,7 +62792,7 @@
     </row>
     <row r="682" spans="1:16">
       <c r="A682" s="2">
-        <v>2040</v>
+        <v>1740</v>
       </c>
       <c r="B682" s="2" t="s">
         <v>3134</v>
@@ -62842,7 +62842,7 @@
     </row>
     <row r="683" spans="1:16">
       <c r="A683" s="2">
-        <v>2041</v>
+        <v>1741</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>3137</v>
@@ -62892,7 +62892,7 @@
     </row>
     <row r="684" spans="1:16">
       <c r="A684" s="2">
-        <v>2042</v>
+        <v>1742</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>3140</v>
@@ -62942,7 +62942,7 @@
     </row>
     <row r="685" spans="1:16">
       <c r="A685" s="2">
-        <v>2043</v>
+        <v>1743</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>3143</v>
@@ -62992,7 +62992,7 @@
     </row>
     <row r="686" spans="1:16">
       <c r="A686" s="2">
-        <v>2044</v>
+        <v>1744</v>
       </c>
       <c r="B686" s="2" t="s">
         <v>3146</v>
@@ -63042,7 +63042,7 @@
     </row>
     <row r="687" spans="1:16">
       <c r="A687" s="2">
-        <v>2045</v>
+        <v>1745</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>3149</v>
@@ -63092,7 +63092,7 @@
     </row>
     <row r="688" spans="1:16">
       <c r="A688" s="2">
-        <v>2046</v>
+        <v>1746</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>3152</v>
@@ -63142,7 +63142,7 @@
     </row>
     <row r="689" spans="1:16">
       <c r="A689" s="2">
-        <v>2047</v>
+        <v>1747</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>3155</v>
@@ -63192,7 +63192,7 @@
     </row>
     <row r="690" spans="1:16">
       <c r="A690" s="2">
-        <v>2048</v>
+        <v>1748</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>3158</v>
@@ -63242,7 +63242,7 @@
     </row>
     <row r="691" spans="1:16">
       <c r="A691" s="2">
-        <v>2049</v>
+        <v>1749</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>3161</v>
@@ -63292,7 +63292,7 @@
     </row>
     <row r="692" spans="1:16">
       <c r="A692" s="2">
-        <v>2050</v>
+        <v>1750</v>
       </c>
       <c r="B692" s="2" t="s">
         <v>3164</v>
@@ -63342,7 +63342,7 @@
     </row>
     <row r="693" spans="1:16">
       <c r="A693" s="2">
-        <v>2051</v>
+        <v>1751</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>3167</v>
@@ -63392,7 +63392,7 @@
     </row>
     <row r="694" spans="1:16">
       <c r="A694" s="2">
-        <v>2052</v>
+        <v>1752</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>3170</v>
@@ -63442,7 +63442,7 @@
     </row>
     <row r="695" spans="1:16">
       <c r="A695" s="2">
-        <v>2053</v>
+        <v>1753</v>
       </c>
       <c r="B695" s="2" t="s">
         <v>3173</v>
@@ -63492,7 +63492,7 @@
     </row>
     <row r="696" spans="1:16">
       <c r="A696" s="2">
-        <v>2054</v>
+        <v>1754</v>
       </c>
       <c r="B696" s="2" t="s">
         <v>3176</v>
@@ -63542,7 +63542,7 @@
     </row>
     <row r="697" spans="1:16">
       <c r="A697" s="2">
-        <v>2055</v>
+        <v>1755</v>
       </c>
       <c r="B697" s="2" t="s">
         <v>3179</v>
@@ -63592,7 +63592,7 @@
     </row>
     <row r="698" spans="1:16">
       <c r="A698" s="2">
-        <v>2056</v>
+        <v>1756</v>
       </c>
       <c r="B698" s="2" t="s">
         <v>3182</v>
@@ -63642,7 +63642,7 @@
     </row>
     <row r="699" spans="1:16">
       <c r="A699" s="2">
-        <v>2057</v>
+        <v>1757</v>
       </c>
       <c r="B699" s="2" t="s">
         <v>3185</v>
@@ -63692,7 +63692,7 @@
     </row>
     <row r="700" spans="1:16">
       <c r="A700" s="2">
-        <v>2058</v>
+        <v>1758</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>3188</v>
@@ -63742,7 +63742,7 @@
     </row>
     <row r="701" spans="1:16">
       <c r="A701" s="2">
-        <v>2059</v>
+        <v>1759</v>
       </c>
       <c r="B701" s="2" t="s">
         <v>3191</v>
@@ -63792,7 +63792,7 @@
     </row>
     <row r="702" spans="1:16">
       <c r="A702" s="2">
-        <v>2060</v>
+        <v>1760</v>
       </c>
       <c r="B702" s="2" t="s">
         <v>3194</v>
@@ -63842,7 +63842,7 @@
     </row>
     <row r="703" spans="1:16">
       <c r="A703" s="2">
-        <v>2061</v>
+        <v>1761</v>
       </c>
       <c r="B703" s="2" t="s">
         <v>3197</v>
@@ -63892,7 +63892,7 @@
     </row>
     <row r="704" spans="1:16">
       <c r="A704" s="2">
-        <v>2062</v>
+        <v>1762</v>
       </c>
       <c r="B704" s="2" t="s">
         <v>3200</v>
@@ -63942,7 +63942,7 @@
     </row>
     <row r="705" spans="1:16">
       <c r="A705" s="2">
-        <v>2063</v>
+        <v>1763</v>
       </c>
       <c r="B705" s="2" t="s">
         <v>3203</v>
@@ -63992,7 +63992,7 @@
     </row>
     <row r="706" spans="1:16">
       <c r="A706" s="2">
-        <v>2064</v>
+        <v>1764</v>
       </c>
       <c r="B706" s="2" t="s">
         <v>3206</v>
@@ -64042,7 +64042,7 @@
     </row>
     <row r="707" spans="1:16">
       <c r="A707" s="2">
-        <v>2065</v>
+        <v>1765</v>
       </c>
       <c r="B707" s="2" t="s">
         <v>3209</v>
@@ -64092,7 +64092,7 @@
     </row>
     <row r="708" spans="1:16">
       <c r="A708" s="2">
-        <v>2066</v>
+        <v>1766</v>
       </c>
       <c r="B708" s="2" t="s">
         <v>3212</v>
@@ -64142,7 +64142,7 @@
     </row>
     <row r="709" spans="1:16">
       <c r="A709" s="2">
-        <v>2067</v>
+        <v>1767</v>
       </c>
       <c r="B709" s="2" t="s">
         <v>3215</v>
@@ -64192,7 +64192,7 @@
     </row>
     <row r="710" spans="1:16">
       <c r="A710" s="2">
-        <v>2068</v>
+        <v>1768</v>
       </c>
       <c r="B710" s="2" t="s">
         <v>3218</v>
@@ -64242,7 +64242,7 @@
     </row>
     <row r="711" spans="1:16">
       <c r="A711" s="2">
-        <v>2069</v>
+        <v>1769</v>
       </c>
       <c r="B711" s="2" t="s">
         <v>3221</v>
@@ -64292,7 +64292,7 @@
     </row>
     <row r="712" spans="1:16">
       <c r="A712" s="2">
-        <v>2070</v>
+        <v>1770</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>3224</v>
@@ -64342,7 +64342,7 @@
     </row>
     <row r="713" spans="1:16">
       <c r="A713" s="2">
-        <v>2071</v>
+        <v>1771</v>
       </c>
       <c r="B713" s="2" t="s">
         <v>3227</v>
@@ -64392,7 +64392,7 @@
     </row>
     <row r="714" spans="1:16">
       <c r="A714" s="2">
-        <v>2072</v>
+        <v>1772</v>
       </c>
       <c r="B714" s="2" t="s">
         <v>3230</v>
@@ -64442,7 +64442,7 @@
     </row>
     <row r="715" spans="1:16">
       <c r="A715" s="2">
-        <v>2073</v>
+        <v>1773</v>
       </c>
       <c r="B715" s="2" t="s">
         <v>3233</v>
@@ -64492,7 +64492,7 @@
     </row>
     <row r="716" spans="1:16">
       <c r="A716" s="2">
-        <v>2074</v>
+        <v>1774</v>
       </c>
       <c r="B716" s="2" t="s">
         <v>3236</v>
@@ -64542,7 +64542,7 @@
     </row>
     <row r="717" spans="1:16">
       <c r="A717" s="2">
-        <v>2075</v>
+        <v>1775</v>
       </c>
       <c r="B717" s="2" t="s">
         <v>3239</v>
@@ -64592,7 +64592,7 @@
     </row>
     <row r="718" spans="1:16">
       <c r="A718" s="2">
-        <v>2076</v>
+        <v>1776</v>
       </c>
       <c r="B718" s="2" t="s">
         <v>3242</v>
@@ -64642,7 +64642,7 @@
     </row>
     <row r="719" spans="1:16">
       <c r="A719" s="2">
-        <v>2077</v>
+        <v>1777</v>
       </c>
       <c r="B719" s="2" t="s">
         <v>3245</v>
@@ -64692,7 +64692,7 @@
     </row>
     <row r="720" spans="1:16">
       <c r="A720" s="2">
-        <v>2078</v>
+        <v>1778</v>
       </c>
       <c r="B720" s="2" t="s">
         <v>3248</v>
@@ -64742,7 +64742,7 @@
     </row>
     <row r="721" spans="1:16">
       <c r="A721" s="2">
-        <v>2079</v>
+        <v>1779</v>
       </c>
       <c r="B721" s="2" t="s">
         <v>3251</v>
@@ -64792,7 +64792,7 @@
     </row>
     <row r="722" spans="1:16">
       <c r="A722" s="2">
-        <v>2080</v>
+        <v>1780</v>
       </c>
       <c r="B722" s="2" t="s">
         <v>3254</v>
@@ -64842,7 +64842,7 @@
     </row>
     <row r="723" spans="1:16">
       <c r="A723" s="2">
-        <v>2081</v>
+        <v>1781</v>
       </c>
       <c r="B723" s="2" t="s">
         <v>3257</v>
@@ -64892,7 +64892,7 @@
     </row>
     <row r="724" spans="1:16">
       <c r="A724" s="2">
-        <v>2082</v>
+        <v>1782</v>
       </c>
       <c r="B724" s="2" t="s">
         <v>3260</v>
@@ -64942,7 +64942,7 @@
     </row>
     <row r="725" spans="1:16">
       <c r="A725" s="2">
-        <v>2083</v>
+        <v>1783</v>
       </c>
       <c r="B725" s="2" t="s">
         <v>3263</v>
@@ -64992,7 +64992,7 @@
     </row>
     <row r="726" spans="1:16">
       <c r="A726" s="2">
-        <v>2084</v>
+        <v>1784</v>
       </c>
       <c r="B726" s="2" t="s">
         <v>3266</v>
@@ -65042,7 +65042,7 @@
     </row>
     <row r="727" spans="1:16">
       <c r="A727" s="2">
-        <v>2085</v>
+        <v>1785</v>
       </c>
       <c r="B727" s="2" t="s">
         <v>3269</v>
@@ -65092,7 +65092,7 @@
     </row>
     <row r="728" spans="1:16">
       <c r="A728" s="2">
-        <v>2086</v>
+        <v>1786</v>
       </c>
       <c r="B728" s="2" t="s">
         <v>3272</v>
@@ -65142,7 +65142,7 @@
     </row>
     <row r="729" spans="1:16">
       <c r="A729" s="2">
-        <v>2087</v>
+        <v>1787</v>
       </c>
       <c r="B729" s="2" t="s">
         <v>3275</v>
@@ -65192,7 +65192,7 @@
     </row>
     <row r="730" spans="1:16">
       <c r="A730" s="2">
-        <v>2088</v>
+        <v>1788</v>
       </c>
       <c r="B730" s="2" t="s">
         <v>3278</v>
@@ -65242,7 +65242,7 @@
     </row>
     <row r="731" spans="1:16">
       <c r="A731" s="2">
-        <v>2089</v>
+        <v>1789</v>
       </c>
       <c r="B731" s="2" t="s">
         <v>3281</v>
@@ -65292,7 +65292,7 @@
     </row>
     <row r="732" spans="1:16">
       <c r="A732" s="2">
-        <v>2090</v>
+        <v>1790</v>
       </c>
       <c r="B732" s="2" t="s">
         <v>3284</v>
@@ -65342,7 +65342,7 @@
     </row>
     <row r="733" spans="1:16">
       <c r="A733" s="2">
-        <v>2091</v>
+        <v>1791</v>
       </c>
       <c r="B733" s="2" t="s">
         <v>3287</v>
@@ -65392,7 +65392,7 @@
     </row>
     <row r="734" spans="1:16">
       <c r="A734" s="2">
-        <v>2092</v>
+        <v>1792</v>
       </c>
       <c r="B734" s="2" t="s">
         <v>3290</v>
@@ -65442,7 +65442,7 @@
     </row>
     <row r="735" spans="1:16">
       <c r="A735" s="2">
-        <v>2093</v>
+        <v>1793</v>
       </c>
       <c r="B735" s="2" t="s">
         <v>3293</v>
@@ -65492,7 +65492,7 @@
     </row>
     <row r="736" spans="1:16">
       <c r="A736" s="2">
-        <v>2094</v>
+        <v>1794</v>
       </c>
       <c r="B736" s="2" t="s">
         <v>3296</v>
@@ -65542,7 +65542,7 @@
     </row>
     <row r="737" spans="1:16">
       <c r="A737" s="2">
-        <v>2095</v>
+        <v>1795</v>
       </c>
       <c r="B737" s="2" t="s">
         <v>3299</v>
@@ -65592,7 +65592,7 @@
     </row>
     <row r="738" spans="1:16">
       <c r="A738" s="2">
-        <v>2096</v>
+        <v>1796</v>
       </c>
       <c r="B738" s="2" t="s">
         <v>3302</v>
@@ -65642,7 +65642,7 @@
     </row>
     <row r="739" spans="1:16">
       <c r="A739" s="2">
-        <v>2097</v>
+        <v>1797</v>
       </c>
       <c r="B739" s="2" t="s">
         <v>3305</v>
@@ -65692,7 +65692,7 @@
     </row>
     <row r="740" spans="1:16">
       <c r="A740" s="2">
-        <v>2098</v>
+        <v>1798</v>
       </c>
       <c r="B740" s="2" t="s">
         <v>3308</v>
@@ -65742,7 +65742,7 @@
     </row>
     <row r="741" spans="1:16">
       <c r="A741" s="2">
-        <v>2099</v>
+        <v>1799</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>3311</v>
@@ -65792,7 +65792,7 @@
     </row>
     <row r="742" spans="1:16">
       <c r="A742" s="2">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="B742" s="2" t="s">
         <v>3314</v>
@@ -65842,7 +65842,7 @@
     </row>
     <row r="743" spans="1:16">
       <c r="A743" s="2">
-        <v>2101</v>
+        <v>1801</v>
       </c>
       <c r="B743" s="2" t="s">
         <v>3317</v>
@@ -65892,7 +65892,7 @@
     </row>
     <row r="744" spans="1:16">
       <c r="A744" s="2">
-        <v>2102</v>
+        <v>1802</v>
       </c>
       <c r="B744" s="2" t="s">
         <v>3320</v>
@@ -65942,7 +65942,7 @@
     </row>
     <row r="745" spans="1:16">
       <c r="A745" s="2">
-        <v>2103</v>
+        <v>1803</v>
       </c>
       <c r="B745" s="2" t="s">
         <v>3323</v>
@@ -65992,7 +65992,7 @@
     </row>
     <row r="746" spans="1:16">
       <c r="A746" s="2">
-        <v>2104</v>
+        <v>1804</v>
       </c>
       <c r="B746" s="2" t="s">
         <v>3326</v>
@@ -66042,7 +66042,7 @@
     </row>
     <row r="747" spans="1:16">
       <c r="A747" s="2">
-        <v>2105</v>
+        <v>1805</v>
       </c>
       <c r="B747" s="2" t="s">
         <v>3329</v>
@@ -66092,7 +66092,7 @@
     </row>
     <row r="748" spans="1:16">
       <c r="A748" s="2">
-        <v>2106</v>
+        <v>1806</v>
       </c>
       <c r="B748" s="2" t="s">
         <v>3332</v>
@@ -66142,7 +66142,7 @@
     </row>
     <row r="749" spans="1:16">
       <c r="A749" s="2">
-        <v>2107</v>
+        <v>1807</v>
       </c>
       <c r="B749" s="2" t="s">
         <v>3335</v>
@@ -66192,7 +66192,7 @@
     </row>
     <row r="750" spans="1:16">
       <c r="A750" s="2">
-        <v>2108</v>
+        <v>1808</v>
       </c>
       <c r="B750" s="2" t="s">
         <v>3338</v>
@@ -66242,7 +66242,7 @@
     </row>
     <row r="751" spans="1:16">
       <c r="A751" s="2">
-        <v>2109</v>
+        <v>1809</v>
       </c>
       <c r="B751" s="2" t="s">
         <v>3341</v>
@@ -66292,7 +66292,7 @@
     </row>
     <row r="752" spans="1:16">
       <c r="A752" s="2">
-        <v>2110</v>
+        <v>1810</v>
       </c>
       <c r="B752" s="2" t="s">
         <v>3344</v>
@@ -66342,7 +66342,7 @@
     </row>
     <row r="753" spans="1:16">
       <c r="A753" s="2">
-        <v>2111</v>
+        <v>1811</v>
       </c>
       <c r="B753" s="2" t="s">
         <v>3347</v>
@@ -66392,7 +66392,7 @@
     </row>
     <row r="754" spans="1:16">
       <c r="A754" s="2">
-        <v>2112</v>
+        <v>1812</v>
       </c>
       <c r="B754" s="2" t="s">
         <v>3350</v>
@@ -66442,7 +66442,7 @@
     </row>
     <row r="755" spans="1:16">
       <c r="A755" s="2">
-        <v>2113</v>
+        <v>1813</v>
       </c>
       <c r="B755" s="2" t="s">
         <v>3353</v>
@@ -66492,7 +66492,7 @@
     </row>
     <row r="756" spans="1:16">
       <c r="A756" s="2">
-        <v>2114</v>
+        <v>1814</v>
       </c>
       <c r="B756" s="2" t="s">
         <v>3356</v>
@@ -66542,7 +66542,7 @@
     </row>
     <row r="757" spans="1:16">
       <c r="A757" s="2">
-        <v>2115</v>
+        <v>1815</v>
       </c>
       <c r="B757" s="2" t="s">
         <v>3359</v>
@@ -66592,7 +66592,7 @@
     </row>
     <row r="758" spans="1:16">
       <c r="A758" s="2">
-        <v>2116</v>
+        <v>1816</v>
       </c>
       <c r="B758" s="2" t="s">
         <v>3362</v>
@@ -66642,7 +66642,7 @@
     </row>
     <row r="759" spans="1:16">
       <c r="A759" s="2">
-        <v>2117</v>
+        <v>1817</v>
       </c>
       <c r="B759" s="2" t="s">
         <v>3365</v>
@@ -66692,7 +66692,7 @@
     </row>
     <row r="760" spans="1:16">
       <c r="A760" s="2">
-        <v>2118</v>
+        <v>1818</v>
       </c>
       <c r="B760" s="2" t="s">
         <v>3368</v>
@@ -66742,7 +66742,7 @@
     </row>
     <row r="761" spans="1:16">
       <c r="A761" s="2">
-        <v>2119</v>
+        <v>1819</v>
       </c>
       <c r="B761" s="2" t="s">
         <v>3371</v>
@@ -66792,7 +66792,7 @@
     </row>
     <row r="762" spans="1:16">
       <c r="A762" s="2">
-        <v>2120</v>
+        <v>1820</v>
       </c>
       <c r="B762" s="2" t="s">
         <v>3374</v>
@@ -66842,7 +66842,7 @@
     </row>
     <row r="763" spans="1:16">
       <c r="A763" s="2">
-        <v>2121</v>
+        <v>1821</v>
       </c>
       <c r="B763" s="2" t="s">
         <v>3377</v>
@@ -66892,7 +66892,7 @@
     </row>
     <row r="764" spans="1:16">
       <c r="A764" s="2">
-        <v>2122</v>
+        <v>1822</v>
       </c>
       <c r="B764" s="2" t="s">
         <v>3380</v>
@@ -66942,7 +66942,7 @@
     </row>
     <row r="765" spans="1:16">
       <c r="A765" s="2">
-        <v>2123</v>
+        <v>1823</v>
       </c>
       <c r="B765" s="2" t="s">
         <v>3383</v>
@@ -66992,7 +66992,7 @@
     </row>
     <row r="766" spans="1:16">
       <c r="A766" s="2">
-        <v>2124</v>
+        <v>1824</v>
       </c>
       <c r="B766" s="2" t="s">
         <v>3386</v>
@@ -67042,7 +67042,7 @@
     </row>
     <row r="767" spans="1:16">
       <c r="A767" s="2">
-        <v>2125</v>
+        <v>1825</v>
       </c>
       <c r="B767" s="2" t="s">
         <v>3389</v>
@@ -67092,7 +67092,7 @@
     </row>
     <row r="768" spans="1:16">
       <c r="A768" s="2">
-        <v>2126</v>
+        <v>1826</v>
       </c>
       <c r="B768" s="2" t="s">
         <v>3392</v>
@@ -67142,7 +67142,7 @@
     </row>
     <row r="769" spans="1:16">
       <c r="A769" s="2">
-        <v>2127</v>
+        <v>1827</v>
       </c>
       <c r="B769" s="2" t="s">
         <v>3395</v>
@@ -67192,7 +67192,7 @@
     </row>
     <row r="770" spans="1:16">
       <c r="A770" s="2">
-        <v>2128</v>
+        <v>1828</v>
       </c>
       <c r="B770" s="2" t="s">
         <v>3398</v>
@@ -67242,7 +67242,7 @@
     </row>
     <row r="771" spans="1:16">
       <c r="A771" s="2">
-        <v>2129</v>
+        <v>1829</v>
       </c>
       <c r="B771" s="2" t="s">
         <v>3401</v>
@@ -67292,7 +67292,7 @@
     </row>
     <row r="772" spans="1:16">
       <c r="A772" s="2">
-        <v>2130</v>
+        <v>1830</v>
       </c>
       <c r="B772" s="2" t="s">
         <v>3404</v>
@@ -67342,7 +67342,7 @@
     </row>
     <row r="773" spans="1:16">
       <c r="A773" s="2">
-        <v>2131</v>
+        <v>1831</v>
       </c>
       <c r="B773" s="2" t="s">
         <v>3407</v>
@@ -67392,7 +67392,7 @@
     </row>
     <row r="774" spans="1:16">
       <c r="A774" s="2">
-        <v>2132</v>
+        <v>1832</v>
       </c>
       <c r="B774" s="2" t="s">
         <v>3410</v>
@@ -67442,7 +67442,7 @@
     </row>
     <row r="775" spans="1:16">
       <c r="A775" s="2">
-        <v>2133</v>
+        <v>1833</v>
       </c>
       <c r="B775" s="2" t="s">
         <v>3413</v>
@@ -67492,7 +67492,7 @@
     </row>
     <row r="776" spans="1:16">
       <c r="A776" s="2">
-        <v>2134</v>
+        <v>1834</v>
       </c>
       <c r="B776" s="2" t="s">
         <v>3416</v>
@@ -67542,7 +67542,7 @@
     </row>
     <row r="777" spans="1:16">
       <c r="A777" s="2">
-        <v>2135</v>
+        <v>1835</v>
       </c>
       <c r="B777" s="2" t="s">
         <v>3419</v>
@@ -67592,7 +67592,7 @@
     </row>
     <row r="778" spans="1:16">
       <c r="A778" s="2">
-        <v>2136</v>
+        <v>1836</v>
       </c>
       <c r="B778" s="2" t="s">
         <v>3422</v>
@@ -67642,7 +67642,7 @@
     </row>
     <row r="779" spans="1:16">
       <c r="A779" s="2">
-        <v>2137</v>
+        <v>1837</v>
       </c>
       <c r="B779" s="2" t="s">
         <v>3425</v>
@@ -67692,7 +67692,7 @@
     </row>
     <row r="780" spans="1:16">
       <c r="A780" s="2">
-        <v>2138</v>
+        <v>1838</v>
       </c>
       <c r="B780" s="2" t="s">
         <v>3428</v>
@@ -67742,7 +67742,7 @@
     </row>
     <row r="781" spans="1:16">
       <c r="A781" s="2">
-        <v>2139</v>
+        <v>1839</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>3431</v>
@@ -67792,7 +67792,7 @@
     </row>
     <row r="782" spans="1:16">
       <c r="A782" s="2">
-        <v>2140</v>
+        <v>1840</v>
       </c>
       <c r="B782" s="2" t="s">
         <v>3434</v>
@@ -67842,7 +67842,7 @@
     </row>
     <row r="783" spans="1:16">
       <c r="A783" s="2">
-        <v>2141</v>
+        <v>1841</v>
       </c>
       <c r="B783" s="2" t="s">
         <v>3437</v>
@@ -67892,7 +67892,7 @@
     </row>
     <row r="784" spans="1:16">
       <c r="A784" s="2">
-        <v>2142</v>
+        <v>1842</v>
       </c>
       <c r="B784" s="2" t="s">
         <v>3440</v>
@@ -67942,7 +67942,7 @@
     </row>
     <row r="785" spans="1:16">
       <c r="A785" s="2">
-        <v>2143</v>
+        <v>1843</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>3443</v>
@@ -67992,7 +67992,7 @@
     </row>
     <row r="786" spans="1:16">
       <c r="A786" s="2">
-        <v>2144</v>
+        <v>1844</v>
       </c>
       <c r="B786" s="2" t="s">
         <v>3446</v>
@@ -68042,7 +68042,7 @@
     </row>
     <row r="787" spans="1:16">
       <c r="A787" s="2">
-        <v>2145</v>
+        <v>1845</v>
       </c>
       <c r="B787" s="2" t="s">
         <v>3449</v>
@@ -68092,7 +68092,7 @@
     </row>
     <row r="788" spans="1:16">
       <c r="A788" s="2">
-        <v>2146</v>
+        <v>1846</v>
       </c>
       <c r="B788" s="2" t="s">
         <v>3452</v>
@@ -68142,7 +68142,7 @@
     </row>
     <row r="789" spans="1:16">
       <c r="A789" s="2">
-        <v>2147</v>
+        <v>1847</v>
       </c>
       <c r="B789" s="2" t="s">
         <v>3455</v>
@@ -68192,7 +68192,7 @@
     </row>
     <row r="790" spans="1:16">
       <c r="A790" s="2">
-        <v>2148</v>
+        <v>1848</v>
       </c>
       <c r="B790" s="2" t="s">
         <v>3458</v>
@@ -68242,7 +68242,7 @@
     </row>
     <row r="791" spans="1:16">
       <c r="A791" s="2">
-        <v>2149</v>
+        <v>1849</v>
       </c>
       <c r="B791" s="2" t="s">
         <v>3461</v>
@@ -68292,7 +68292,7 @@
     </row>
     <row r="792" spans="1:16">
       <c r="A792" s="2">
-        <v>2150</v>
+        <v>1850</v>
       </c>
       <c r="B792" s="2" t="s">
         <v>3464</v>
@@ -68342,7 +68342,7 @@
     </row>
     <row r="793" spans="1:16">
       <c r="A793" s="2">
-        <v>2151</v>
+        <v>1851</v>
       </c>
       <c r="B793" s="2" t="s">
         <v>3467</v>
@@ -68392,7 +68392,7 @@
     </row>
     <row r="794" spans="1:16">
       <c r="A794" s="2">
-        <v>2152</v>
+        <v>1852</v>
       </c>
       <c r="B794" s="2" t="s">
         <v>3470</v>
@@ -68442,7 +68442,7 @@
     </row>
     <row r="795" spans="1:16">
       <c r="A795" s="2">
-        <v>2153</v>
+        <v>1853</v>
       </c>
       <c r="B795" s="2" t="s">
         <v>3473</v>
@@ -68492,7 +68492,7 @@
     </row>
     <row r="796" spans="1:16">
       <c r="A796" s="2">
-        <v>2154</v>
+        <v>1854</v>
       </c>
       <c r="B796" s="2" t="s">
         <v>3476</v>
@@ -68542,7 +68542,7 @@
     </row>
     <row r="797" spans="1:16">
       <c r="A797" s="2">
-        <v>2155</v>
+        <v>1855</v>
       </c>
       <c r="B797" s="2" t="s">
         <v>3479</v>
@@ -68592,7 +68592,7 @@
     </row>
     <row r="798" spans="1:16">
       <c r="A798" s="2">
-        <v>2156</v>
+        <v>1856</v>
       </c>
       <c r="B798" s="2" t="s">
         <v>3482</v>
@@ -68642,7 +68642,7 @@
     </row>
     <row r="799" spans="1:16">
       <c r="A799" s="2">
-        <v>2157</v>
+        <v>1857</v>
       </c>
       <c r="B799" s="2" t="s">
         <v>3485</v>
@@ -68692,7 +68692,7 @@
     </row>
     <row r="800" spans="1:16">
       <c r="A800" s="2">
-        <v>2158</v>
+        <v>1858</v>
       </c>
       <c r="B800" s="2" t="s">
         <v>3488</v>
@@ -68742,7 +68742,7 @@
     </row>
     <row r="801" spans="1:16">
       <c r="A801" s="2">
-        <v>2159</v>
+        <v>1859</v>
       </c>
       <c r="B801" s="2" t="s">
         <v>3491</v>
@@ -68792,7 +68792,7 @@
     </row>
     <row r="802" spans="1:16">
       <c r="A802" s="2">
-        <v>2160</v>
+        <v>1860</v>
       </c>
       <c r="B802" s="2" t="s">
         <v>3494</v>
@@ -68842,7 +68842,7 @@
     </row>
     <row r="803" spans="1:16">
       <c r="A803" s="2">
-        <v>2161</v>
+        <v>1861</v>
       </c>
       <c r="B803" s="2" t="s">
         <v>3497</v>
@@ -68892,7 +68892,7 @@
     </row>
     <row r="804" spans="1:16">
       <c r="A804" s="2">
-        <v>2162</v>
+        <v>1862</v>
       </c>
       <c r="B804" s="2" t="s">
         <v>3500</v>
@@ -68942,7 +68942,7 @@
     </row>
     <row r="805" spans="1:16">
       <c r="A805" s="2">
-        <v>2163</v>
+        <v>1863</v>
       </c>
       <c r="B805" s="2" t="s">
         <v>3503</v>
@@ -68992,7 +68992,7 @@
     </row>
     <row r="806" spans="1:16">
       <c r="A806" s="2">
-        <v>2164</v>
+        <v>1864</v>
       </c>
       <c r="B806" s="2" t="s">
         <v>3506</v>
@@ -69042,7 +69042,7 @@
     </row>
     <row r="807" spans="1:16">
       <c r="A807" s="2">
-        <v>2165</v>
+        <v>1865</v>
       </c>
       <c r="B807" s="2" t="s">
         <v>3509</v>
@@ -69092,7 +69092,7 @@
     </row>
     <row r="808" spans="1:16">
       <c r="A808" s="2">
-        <v>2166</v>
+        <v>1866</v>
       </c>
       <c r="B808" s="2" t="s">
         <v>3512</v>
@@ -69142,7 +69142,7 @@
     </row>
     <row r="809" spans="1:16">
       <c r="A809" s="2">
-        <v>2167</v>
+        <v>1867</v>
       </c>
       <c r="B809" s="2" t="s">
         <v>3515</v>
@@ -69192,7 +69192,7 @@
     </row>
     <row r="810" spans="1:16">
       <c r="A810" s="2">
-        <v>2168</v>
+        <v>1868</v>
       </c>
       <c r="B810" s="2" t="s">
         <v>3518</v>
@@ -69242,7 +69242,7 @@
     </row>
     <row r="811" spans="1:16">
       <c r="A811" s="2">
-        <v>2169</v>
+        <v>1869</v>
       </c>
       <c r="B811" s="2" t="s">
         <v>3521</v>
@@ -69292,7 +69292,7 @@
     </row>
     <row r="812" spans="1:16">
       <c r="A812" s="2">
-        <v>2170</v>
+        <v>1870</v>
       </c>
       <c r="B812" s="2" t="s">
         <v>3524</v>
@@ -69342,7 +69342,7 @@
     </row>
     <row r="813" spans="1:16">
       <c r="A813" s="2">
-        <v>2171</v>
+        <v>1871</v>
       </c>
       <c r="B813" s="2" t="s">
         <v>3527</v>
@@ -69392,7 +69392,7 @@
     </row>
     <row r="814" spans="1:16">
       <c r="A814" s="2">
-        <v>2172</v>
+        <v>1872</v>
       </c>
       <c r="B814" s="2" t="s">
         <v>3530</v>
@@ -69442,7 +69442,7 @@
     </row>
     <row r="815" spans="1:16">
       <c r="A815" s="2">
-        <v>2173</v>
+        <v>1873</v>
       </c>
       <c r="B815" s="2" t="s">
         <v>3533</v>
@@ -69492,7 +69492,7 @@
     </row>
     <row r="816" spans="1:16">
       <c r="A816" s="2">
-        <v>2174</v>
+        <v>1874</v>
       </c>
       <c r="B816" s="2" t="s">
         <v>3536</v>
@@ -69542,7 +69542,7 @@
     </row>
     <row r="817" spans="1:16">
       <c r="A817" s="2">
-        <v>2175</v>
+        <v>1875</v>
       </c>
       <c r="B817" s="2" t="s">
         <v>3539</v>
@@ -69592,7 +69592,7 @@
     </row>
     <row r="818" spans="1:16">
       <c r="A818" s="2">
-        <v>2176</v>
+        <v>1876</v>
       </c>
       <c r="B818" s="2" t="s">
         <v>3542</v>
@@ -69642,7 +69642,7 @@
     </row>
     <row r="819" spans="1:16">
       <c r="A819" s="2">
-        <v>2177</v>
+        <v>1877</v>
       </c>
       <c r="B819" s="2" t="s">
         <v>3545</v>
@@ -69692,7 +69692,7 @@
     </row>
     <row r="820" spans="1:16">
       <c r="A820" s="2">
-        <v>2178</v>
+        <v>1878</v>
       </c>
       <c r="B820" s="2" t="s">
         <v>3548</v>
@@ -69742,7 +69742,7 @@
     </row>
     <row r="821" spans="1:16">
       <c r="A821" s="2">
-        <v>2179</v>
+        <v>1879</v>
       </c>
       <c r="B821" s="2" t="s">
         <v>3551</v>
@@ -69792,7 +69792,7 @@
     </row>
     <row r="822" spans="1:16">
       <c r="A822" s="2">
-        <v>2180</v>
+        <v>1880</v>
       </c>
       <c r="B822" s="2" t="s">
         <v>3554</v>
@@ -69842,7 +69842,7 @@
     </row>
     <row r="823" spans="1:16">
       <c r="A823" s="2">
-        <v>2181</v>
+        <v>1881</v>
       </c>
       <c r="B823" s="2" t="s">
         <v>3557</v>
@@ -69892,7 +69892,7 @@
     </row>
     <row r="824" spans="1:16">
       <c r="A824" s="2">
-        <v>2182</v>
+        <v>1882</v>
       </c>
       <c r="B824" s="2" t="s">
         <v>3560</v>
@@ -69942,7 +69942,7 @@
     </row>
     <row r="825" spans="1:16">
       <c r="A825" s="2">
-        <v>2183</v>
+        <v>1883</v>
       </c>
       <c r="B825" s="2" t="s">
         <v>3563</v>
@@ -69992,7 +69992,7 @@
     </row>
     <row r="826" spans="1:16">
       <c r="A826" s="2">
-        <v>2184</v>
+        <v>1884</v>
       </c>
       <c r="B826" s="2" t="s">
         <v>3566</v>
@@ -70042,7 +70042,7 @@
     </row>
     <row r="827" spans="1:16">
       <c r="A827" s="2">
-        <v>2185</v>
+        <v>1885</v>
       </c>
       <c r="B827" s="2" t="s">
         <v>3569</v>
@@ -70092,7 +70092,7 @@
     </row>
     <row r="828" spans="1:16">
       <c r="A828" s="2">
-        <v>2186</v>
+        <v>1886</v>
       </c>
       <c r="B828" s="2" t="s">
         <v>3572</v>
@@ -70142,7 +70142,7 @@
     </row>
     <row r="829" spans="1:16">
       <c r="A829" s="2">
-        <v>2187</v>
+        <v>1887</v>
       </c>
       <c r="B829" s="2" t="s">
         <v>3575</v>
@@ -70192,7 +70192,7 @@
     </row>
     <row r="830" spans="1:16">
       <c r="A830" s="2">
-        <v>2188</v>
+        <v>1888</v>
       </c>
       <c r="B830" s="2" t="s">
         <v>3578</v>
@@ -70242,7 +70242,7 @@
     </row>
     <row r="831" spans="1:16">
       <c r="A831" s="2">
-        <v>2189</v>
+        <v>1889</v>
       </c>
       <c r="B831" s="2" t="s">
         <v>3581</v>
